--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="353">
   <si>
     <t xml:space="preserve">Nombre del producto</t>
   </si>
@@ -70,9 +70,6 @@
     <t xml:space="preserve">200 ml</t>
   </si>
   <si>
-    <t xml:space="preserve">Para pieles grasas, mixtas, secas y normales.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0001</t>
   </si>
   <si>
@@ -94,9 +91,6 @@
     <t xml:space="preserve">200 cm3</t>
   </si>
   <si>
-    <t xml:space="preserve">Agua micelar 5 en 1 para todo tipo de piel con Extracto de Rosa Centifolia (1%) y Elastina. Retira maquillaje a prueba de agua e impurezas.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0002</t>
   </si>
   <si>
@@ -115,9 +109,6 @@
     <t xml:space="preserve">DB-LIM-003</t>
   </si>
   <si>
-    <t xml:space="preserve">Agua micelar 4 en 1 con Extracto de Oryza Sativa (1%), Extracto de Cucumis Sativus y D-Panthenol. Limpia, calma e ilumina.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0003</t>
   </si>
   <si>
@@ -139,9 +130,6 @@
     <t xml:space="preserve">Tónicos y Aguas Faciales</t>
   </si>
   <si>
-    <t xml:space="preserve">Bruma tonificante facial con Extracto de Rosa Centifolia (2,5%), Ácido Hialurónico y D-Panthenol. Aporta firmeza, elasticidad e hidratación.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0010</t>
   </si>
   <si>
@@ -160,9 +148,6 @@
     <t xml:space="preserve">DB-LIM-005</t>
   </si>
   <si>
-    <t xml:space="preserve">Bálsamo desmaquillante con Aceite de Uva (1%), Jojoba (1%), Almendras (0,50%) y Manteca de Karité (0,50%).</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0005</t>
   </si>
   <si>
@@ -181,9 +166,6 @@
     <t xml:space="preserve">DB-LIM-004</t>
   </si>
   <si>
-    <t xml:space="preserve">Leche limpiadora con Niacinamida (0,5%), Extracto de Aloe Barbadensis, Extracto de Cucumis Sativus y D-Panthenol. Limpia, refresca y calma.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0004</t>
   </si>
   <si>
@@ -205,9 +187,6 @@
     <t xml:space="preserve">Tratamiento Facial</t>
   </si>
   <si>
-    <t xml:space="preserve">Bálsamo labial con Ácido Hialurónico (0,5%), D-Panthenol (0,5%) y Vitamina E (0,1%). Previene la resequedad y repara labios.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0030</t>
   </si>
   <si>
@@ -226,9 +205,6 @@
     <t xml:space="preserve">DB-TRA-004</t>
   </si>
   <si>
-    <t xml:space="preserve">Crema/gel de contorno de ojos con Resveratrol (1%), Cafeína y Colágeno. Reduce bolsas, ojeras y arrugas.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0017</t>
   </si>
   <si>
@@ -247,9 +223,6 @@
     <t xml:space="preserve">DB-TRA-005</t>
   </si>
   <si>
-    <t xml:space="preserve">Crema para tratamiento de hiperpigmentaciones y manchas con Ácido Kójico (1%). Uso nocturno.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0018</t>
   </si>
   <si>
@@ -268,9 +241,6 @@
     <t xml:space="preserve">DB-TRA-016</t>
   </si>
   <si>
-    <t xml:space="preserve">Crema facial diurna con Ácido Hialurónico (1,5%), Escualano (1%), Rosa Damascena (3%) y Camellia Sinensis (5%).</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0029</t>
   </si>
   <si>
@@ -307,9 +277,6 @@
     <t xml:space="preserve">DB-TRA-003</t>
   </si>
   <si>
-    <t xml:space="preserve">Exfoliante facial con Carbón Activado (1%), Cafeína y Aceite de Almendras Dulces. Absorbe impurezas y toxinas.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0016</t>
   </si>
   <si>
@@ -328,9 +295,6 @@
     <t xml:space="preserve">DB-TRA-015</t>
   </si>
   <si>
-    <t xml:space="preserve">Gel para aplicación puntual con Ácido Glicólico (1%), Ácido Salicílico (0,5%) y Ácido Hialurónico (0,5%). Remueve puntos negros y comedones.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0028</t>
   </si>
   <si>
@@ -349,9 +313,6 @@
     <t xml:space="preserve">DB-TRA-019</t>
   </si>
   <si>
-    <t xml:space="preserve">Pads de gel faciales con PDRN Vegetal (0,10%), Péptidos (1%) y Colágeno (1,5%). 80 pads.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0032</t>
   </si>
   <si>
@@ -370,9 +331,6 @@
     <t xml:space="preserve">DB-TRA-020</t>
   </si>
   <si>
-    <t xml:space="preserve">Pads de gel para piel sensible con Ácido Hialurónico (1,5%), Centella Asiática (0,5%) y Electrolitos (90%). 80 pads.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0033</t>
   </si>
   <si>
@@ -391,9 +349,6 @@
     <t xml:space="preserve">DB-TRA-021</t>
   </si>
   <si>
-    <t xml:space="preserve">Pads de gel exfoliante y seborregulador nocturno con PHA (5%), Gluconolactona y Ácido Lactobiónico. 80 pads.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0034</t>
   </si>
   <si>
@@ -412,9 +367,6 @@
     <t xml:space="preserve">DB-TRA-018</t>
   </si>
   <si>
-    <t xml:space="preserve">Pads de gel descongestivos con Cafeína (0,5%), Camellia Sinensis (3%) y Ácido Hialurónico (0,75%). 80 pads.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0031</t>
   </si>
   <si>
@@ -433,9 +385,6 @@
     <t xml:space="preserve">DB-TRA-008</t>
   </si>
   <si>
-    <t xml:space="preserve">Sérum peeling químico con Ácido Glicólico (5%), Ácido Hialurónico (1%) y Vitamina E (0,5%). Peeling controlado y renovador.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0021</t>
   </si>
   <si>
@@ -454,9 +403,6 @@
     <t xml:space="preserve">DB-TRA-007</t>
   </si>
   <si>
-    <t xml:space="preserve">Sérum facial con Ácido Hialurónico (1%) y Vitamina C (8%). Aporta firmeza, elasticidad y luminosidad.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0020</t>
   </si>
   <si>
@@ -475,9 +421,6 @@
     <t xml:space="preserve">DB-TRA-013</t>
   </si>
   <si>
-    <t xml:space="preserve">Sérum con Complejo de Aminoácidos (1%) y Provitamina B5 (0,5%). Síntesis de colágeno y firmeza para la piel.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0026</t>
   </si>
   <si>
@@ -496,9 +439,6 @@
     <t xml:space="preserve">DB-TRA-012</t>
   </si>
   <si>
-    <t xml:space="preserve">Sérum regenerador con Células Madre (3%), Ácido Hialurónico (1%) y Alantoína (0,5%). Reparación y nutrición de pieles sensibles.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0025</t>
   </si>
   <si>
@@ -517,9 +457,6 @@
     <t xml:space="preserve">DB-TRA-009</t>
   </si>
   <si>
-    <t xml:space="preserve">Sérum con Complejo de Péptidos (5%), Cica (0,25%), Colágeno (0,25%) y Ácido Hialurónico (0,25%). Reafirma el óvalo facial.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0022</t>
   </si>
   <si>
@@ -538,9 +475,6 @@
     <t xml:space="preserve">DB-TRA-014</t>
   </si>
   <si>
-    <t xml:space="preserve">Sérum exfoliante con Ácido Láctico (5%), Ácido Salicílico (0,5%) y Ácido Hialurónico (1%). Renueva la piel y limpia poros.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0027</t>
   </si>
   <si>
@@ -559,9 +493,6 @@
     <t xml:space="preserve">DB-TRA-006</t>
   </si>
   <si>
-    <t xml:space="preserve">Sérum facial con Niacinamida (10%) y Zinc (1%). Equilibra el exceso de grasa, unifica el tono y reduce el acné.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0019</t>
   </si>
   <si>
@@ -580,9 +511,6 @@
     <t xml:space="preserve">DB-TRA-010</t>
   </si>
   <si>
-    <t xml:space="preserve">Sérum con Probióticos + Postbióticos (5%), D-Panthenol (1%) y Vitamina E (0,5%). Equilibra la barrera cutánea.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0023</t>
   </si>
   <si>
@@ -601,9 +529,6 @@
     <t xml:space="preserve">DB-TRA-011</t>
   </si>
   <si>
-    <t xml:space="preserve">Sérum antiedad con Retinol Nanosomado (1%) y Ácido Hialurónico (0,5%). Reduce arrugas profundas y manchas solares.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0024</t>
   </si>
   <si>
@@ -625,9 +550,6 @@
     <t xml:space="preserve">Cuidado Corporal</t>
   </si>
   <si>
-    <t xml:space="preserve">Gel refrescante e hidratante con Aloe Vera, Alfa Bisabolol, Camellia Sinensis, Alpha Tocopherol y Agua Termal Dernier.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0054</t>
   </si>
   <si>
@@ -646,9 +568,6 @@
     <t xml:space="preserve">DB-COR-046</t>
   </si>
   <si>
-    <t xml:space="preserve">Solución esterilizante de superficies bactericida, fungicida y virucida con Alcohol al 70% V/V.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0098</t>
   </si>
   <si>
@@ -667,9 +586,6 @@
     <t xml:space="preserve">DB-COR-008</t>
   </si>
   <si>
-    <t xml:space="preserve">Antitranspirante masculino con Clorhidróxido de Aluminio, Caléndula, Manzanilla y Alumbre de Amonio.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0060</t>
   </si>
   <si>
@@ -688,9 +604,6 @@
     <t xml:space="preserve">DB-COR-007</t>
   </si>
   <si>
-    <t xml:space="preserve">Antitranspirante con Clorhidróxido de Aluminio, Extracto de Caléndula, Manzanilla y Alumbre de Amonio.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0059</t>
   </si>
   <si>
@@ -703,9 +616,6 @@
     <t xml:space="preserve">DB-COR-006</t>
   </si>
   <si>
-    <t xml:space="preserve">Gel analgésico y calmante con Alcanfor, Mentol, Extracto de Árnica Montana, Aloe Vera y Fucus Vesiculosus.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0058</t>
   </si>
   <si>
@@ -724,9 +634,6 @@
     <t xml:space="preserve">DB-COR-001</t>
   </si>
   <si>
-    <t xml:space="preserve">Bronceador con Vitamina E (Tocopheryl Acetate) y Extracto de Zanahoria (Betacaroteno) para un bronceado uniforme.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0053</t>
   </si>
   <si>
@@ -745,27 +652,24 @@
     <t xml:space="preserve">DB-COR-045</t>
   </si>
   <si>
+    <t xml:space="preserve">IMG-0097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0097.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vierte 20 mililitros (aproximadamente 4 cucharadas) de enjuague bucal en un vaso. Enjuaga la boca con el líquido durante 30 segundos, asegurándote de que pase por todas las áreas de la boca. Escupe el enjuague bucal en el lavabo. No tragar. Usar dos veces al día, preferiblemente después del cepillado matutino y nocturno.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Enjuague bucal contra caries y placa bacteriana sin alcohol sabor a menta fresca.</t>
   </si>
   <si>
-    <t xml:space="preserve">IMG-0097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0097.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vierte 20 mililitros (aproximadamente 4 cucharadas) de enjuague bucal en un vaso. Enjuaga la boca con el líquido durante 30 segundos, asegurándote de que pase por todas las áreas de la boca. Escupe el enjuague bucal en el lavabo. No tragar. Usar dos veces al día, preferiblemente después del cepillado matutino y nocturno.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gel Antibacterial Dernier Skinsept</t>
   </si>
   <si>
     <t xml:space="preserve">DB-COR-047</t>
   </si>
   <si>
-    <t xml:space="preserve">Gel antibacterial con 62% Alcohol, Cloruro de Benzalconio, Vitamina E y Aloe Vera. Elimina 99,9% de gérmenes.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0099</t>
   </si>
   <si>
@@ -784,9 +688,6 @@
     <t xml:space="preserve">DB-COR-005</t>
   </si>
   <si>
-    <t xml:space="preserve">Gel muscular analgésico y antiinflamatorio con Alcanfor, Mentol, Salicilato de Metilo y Aloe Vera.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0057</t>
   </si>
   <si>
@@ -805,9 +706,6 @@
     <t xml:space="preserve">DB-COR-003</t>
   </si>
   <si>
-    <t xml:space="preserve">Repelente de insectos natural con Geraniol y Citronella. Protección duradera no grasosa.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0055</t>
   </si>
   <si>
@@ -826,9 +724,6 @@
     <t xml:space="preserve">DB-COR-010</t>
   </si>
   <si>
-    <t xml:space="preserve">Sérum corporal antiedad con Colágeno, Ácido Hialurónico y Retinal. Mejora firmeza y elasticidad.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0062</t>
   </si>
   <si>
@@ -847,9 +742,6 @@
     <t xml:space="preserve">DB-COR-009</t>
   </si>
   <si>
-    <t xml:space="preserve">Sérum corporal con PHA, Vitamina C y Niacinamida. Tecnología Neuroderm Drone Technology.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0061</t>
   </si>
   <si>
@@ -868,9 +760,6 @@
     <t xml:space="preserve">DB-COR-011</t>
   </si>
   <si>
-    <t xml:space="preserve">Sérum corporal efecto tensor con PDRN, CICA y Péptidos. Redefine el contorno corporal.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0063</t>
   </si>
   <si>
@@ -889,9 +778,6 @@
     <t xml:space="preserve">DB-COR-004</t>
   </si>
   <si>
-    <t xml:space="preserve">Jabón íntimo con Chamomilla Recutita, Aloe Barbadensis y Glicerina. Control de olor y pH adecuado.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0056</t>
   </si>
   <si>
@@ -907,9 +793,6 @@
     <t xml:space="preserve">DB-INF-001</t>
   </si>
   <si>
-    <t xml:space="preserve">Solución limpiadora hipoalergénica con Aloe Vera y Vitamina E, sin colorantes y con pH equilibrado.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0101</t>
   </si>
   <si>
@@ -931,9 +814,6 @@
     <t xml:space="preserve">Maquillaje</t>
   </si>
   <si>
-    <t xml:space="preserve">Base/corrector en barra con acabado efecto filtro con Ácido Hialurónico, CICA y Óxido de Zinc. Tono Dark.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0052</t>
   </si>
   <si>
@@ -952,9 +832,6 @@
     <t xml:space="preserve">DB-MAQ-001</t>
   </si>
   <si>
-    <t xml:space="preserve">Base/corrector en barra con acabado efecto filtro con Ácido Hialurónico, CICA y Óxido de Zinc. Tono Light.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0050</t>
   </si>
   <si>
@@ -967,9 +844,6 @@
     <t xml:space="preserve">DB-MAQ-002</t>
   </si>
   <si>
-    <t xml:space="preserve">Base/corrector en barra con acabado efecto filtro con Ácido Hialurónico, CICA y Óxido de Zinc. Tono Medium.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0051</t>
   </si>
   <si>
@@ -985,9 +859,6 @@
     <t xml:space="preserve">Protección Solar</t>
   </si>
   <si>
-    <t xml:space="preserve">Protector solar para bebés con filtros minerales naturales (dióxido de titanio y óxido de zinc) y Extracto de Aloe Vera.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0046</t>
   </si>
   <si>
@@ -1006,9 +877,6 @@
     <t xml:space="preserve">DB-SOL-006</t>
   </si>
   <si>
-    <t xml:space="preserve">Protector solar aerosol 360° con Aloe Vera, Alfa Bisabolol, Ácido Hialurónico, Alfa Tocoferol y D-Panthenol.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0045</t>
   </si>
   <si>
@@ -1027,9 +895,6 @@
     <t xml:space="preserve">DB-SOL-004</t>
   </si>
   <si>
-    <t xml:space="preserve">Protector solar en polvo con brocha dispensadora en tonos Translúcido, Light, Medium y Dark. Efecto mate, resistente al agua.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0043</t>
   </si>
   <si>
@@ -1048,9 +913,6 @@
     <t xml:space="preserve">DB-SOL-003</t>
   </si>
   <si>
-    <t xml:space="preserve">Protector solar en gel con Matcha Tea Extract, Alfa Bisabolol, D-Panthenol, Hyaluronic Acid y Agua Termal Dernier.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0042</t>
   </si>
   <si>
@@ -1069,9 +931,6 @@
     <t xml:space="preserve">DB-SOL-002</t>
   </si>
   <si>
-    <t xml:space="preserve">Protector solar facial con mezcla de filtros UV físicos y químicos, D-Panthenol, emolientes y emulsificantes.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0041</t>
   </si>
   <si>
@@ -1090,9 +949,6 @@
     <t xml:space="preserve">DB-SOL-005</t>
   </si>
   <si>
-    <t xml:space="preserve">Protector solar en crema y spray con filtros UV físicos/químicos y Extracto de Aloe Vera. Fotoprotector e hidratante.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0044</t>
   </si>
   <si>
@@ -1111,9 +967,6 @@
     <t xml:space="preserve">DB-SOL-001</t>
   </si>
   <si>
-    <t xml:space="preserve">Sérum facial con Complejo de Filtros UVA/UVB, Complejo de Péptidos (1%), Colágeno Hidrolizado, Coenzima Q10 y Ácido Hialurónico.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0040</t>
   </si>
   <si>
@@ -1135,9 +988,6 @@
     <t xml:space="preserve">Cuidado Infantil</t>
   </si>
   <si>
-    <t xml:space="preserve">Aceite cremoso hidratante para bebés con Aloe Vera y Vitamina E. Textura ligera de rápida absorción.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0104</t>
   </si>
   <si>
@@ -1153,27 +1003,24 @@
     <t xml:space="preserve">DB-INF-005</t>
   </si>
   <si>
+    <t xml:space="preserve">IMG-0105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0105.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplique directamente sobre la piel del bebé después del baño o en cualquier momento que desee otorgar frescura a su piel.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Colonia infantil suave sin alcohol, sin parabenos ni colorantes. Hipoalergénica.</t>
   </si>
   <si>
-    <t xml:space="preserve">IMG-0105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0105.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplique directamente sobre la piel del bebé después del baño o en cualquier momento que desee otorgar frescura a su piel.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Crema Antipañalitis Baby</t>
   </si>
   <si>
     <t xml:space="preserve">DB-INF-003</t>
   </si>
   <si>
-    <t xml:space="preserve">Crema protectora para el área del pañal con Óxido de Zinc. Calma, alivia la irritación e hipoalergénica.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0103</t>
   </si>
   <si>
@@ -1192,27 +1039,24 @@
     <t xml:space="preserve">DB-INF-007</t>
   </si>
   <si>
+    <t xml:space="preserve">IMG-0107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0107.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vierte 10 mililitros (aproximadamente 2 cucharadas) de enjuague bucal en un vaso. Enjuaga la boca con el líquido durante 30 segundos, asegurándote de que pase por todas las áreas de la boca. Escupa el enjuague bucal en el lavabo. No tragar. Usar una vez al día, preferiblemente después del cepillado nocturno.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Enjuague bucal infantil sin alcohol con sabor a cereza. Protección contra las caries.</t>
   </si>
   <si>
-    <t xml:space="preserve">IMG-0107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0107.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vierte 10 mililitros (aproximadamente 2 cucharadas) de enjuague bucal en un vaso. Enjuaga la boca con el líquido durante 30 segundos, asegurándote de que pase por todas las áreas de la boca. Escupa el enjuague bucal en el lavabo. No tragar. Usar una vez al día, preferiblemente después del cepillado nocturno.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Repelente de Insectos Baby (Spray / Loción)</t>
   </si>
   <si>
     <t xml:space="preserve">DB-INF-006</t>
   </si>
   <si>
-    <t xml:space="preserve">Repelente natural libre de DEET con extractos de Geraniol y Citronella. Seguro para bebés e hipoalergénico.</t>
-  </si>
-  <si>
     <t xml:space="preserve">IMG-0106</t>
   </si>
   <si>
@@ -1225,16 +1069,16 @@
     <t xml:space="preserve">DB-INF-002</t>
   </si>
   <si>
+    <t xml:space="preserve">IMG-0102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0102.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplique una pequeña cantidad directamente sobre el cabello del niño y extienda sobre el área con delicados movimientos circulares, hasta lograr la espuma deseada, luego enjuague con abundante agua.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Champú infantil fórmula suave sin lágrimas, hipoalergénico, pH neutro, libre de sulfatos y parabenos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0102.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplique una pequeña cantidad directamente sobre el cabello del niño y extienda sobre el área con delicados movimientos circulares, hasta lograr la espuma deseada, luego enjuague con abundante agua.</t>
   </si>
 </sst>
 </file>
@@ -1270,6 +1114,7 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1457,10 +1302,13 @@
   <dimension ref="A1:K58"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="43.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="43.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="118.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="118.44"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="9" min="7" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="0" width="296.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="115.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1514,336 +1362,316 @@
       <c r="E2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="2"/>
+      <c r="G4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
-        <v>53</v>
-      </c>
+      <c r="F7" s="2"/>
       <c r="G7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
-        <v>68</v>
-      </c>
+      <c r="F9" s="2"/>
       <c r="G9" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="2" t="s">
-        <v>75</v>
-      </c>
+      <c r="F10" s="2"/>
       <c r="G10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="2" t="s">
-        <v>82</v>
-      </c>
+      <c r="F11" s="2"/>
       <c r="G11" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -1851,1522 +1679,1442 @@
         <v>3</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="2" t="s">
-        <v>95</v>
-      </c>
+      <c r="F13" s="2"/>
       <c r="G13" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E14" s="2"/>
-      <c r="F14" s="2" t="s">
-        <v>102</v>
-      </c>
+      <c r="F14" s="2"/>
       <c r="G14" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="2" t="s">
-        <v>109</v>
-      </c>
+      <c r="F15" s="2"/>
       <c r="G15" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="2" t="s">
-        <v>116</v>
-      </c>
+      <c r="F16" s="2"/>
       <c r="G16" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="F17" s="2" t="s">
-        <v>123</v>
-      </c>
+      <c r="F17" s="2"/>
       <c r="G17" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E18" s="2"/>
-      <c r="F18" s="2" t="s">
-        <v>130</v>
-      </c>
+      <c r="F18" s="2"/>
       <c r="G18" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E19" s="2"/>
-      <c r="F19" s="2" t="s">
-        <v>137</v>
-      </c>
+      <c r="F19" s="2"/>
       <c r="G19" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E20" s="2"/>
-      <c r="F20" s="2" t="s">
-        <v>144</v>
-      </c>
+      <c r="F20" s="2"/>
       <c r="G20" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E21" s="2"/>
-      <c r="F21" s="2" t="s">
-        <v>151</v>
-      </c>
+      <c r="F21" s="2"/>
       <c r="G21" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E22" s="2"/>
-      <c r="F22" s="2" t="s">
-        <v>158</v>
-      </c>
+      <c r="F22" s="2"/>
       <c r="G22" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="2" t="s">
-        <v>165</v>
-      </c>
+      <c r="F23" s="2"/>
       <c r="G23" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="2" t="s">
-        <v>172</v>
-      </c>
+      <c r="F24" s="2"/>
       <c r="G24" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E25" s="2"/>
-      <c r="F25" s="2" t="s">
-        <v>179</v>
-      </c>
+      <c r="F25" s="2"/>
       <c r="G25" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="2" t="s">
-        <v>186</v>
-      </c>
+      <c r="F26" s="2"/>
       <c r="G26" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E27" s="2"/>
-      <c r="F27" s="2" t="s">
-        <v>193</v>
-      </c>
+      <c r="F27" s="2"/>
       <c r="G27" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E28" s="2"/>
-      <c r="F28" s="2" t="s">
-        <v>201</v>
-      </c>
+      <c r="F28" s="2"/>
       <c r="G28" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E29" s="2"/>
-      <c r="F29" s="2" t="s">
-        <v>208</v>
-      </c>
+      <c r="F29" s="2"/>
       <c r="G29" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>210</v>
+        <v>183</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E30" s="2"/>
-      <c r="F30" s="2" t="s">
-        <v>215</v>
-      </c>
+      <c r="F30" s="2"/>
       <c r="G30" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>220</v>
+        <v>192</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E31" s="2"/>
-      <c r="F31" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="F31" s="2"/>
       <c r="G31" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="K32" s="2" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E33" s="2"/>
-      <c r="F33" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="F33" s="2"/>
       <c r="G33" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>235</v>
+        <v>204</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>240</v>
+        <v>209</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E34" s="2"/>
-      <c r="F34" s="2" t="s">
-        <v>241</v>
-      </c>
+      <c r="F34" s="2"/>
       <c r="G34" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>244</v>
+        <v>212</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>246</v>
+        <v>215</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E35" s="2"/>
-      <c r="F35" s="2" t="s">
-        <v>247</v>
-      </c>
+      <c r="F35" s="2"/>
       <c r="G35" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>249</v>
+        <v>217</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>251</v>
+        <v>219</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>253</v>
+        <v>221</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E36" s="2"/>
-      <c r="F36" s="2" t="s">
-        <v>254</v>
-      </c>
+      <c r="F36" s="2"/>
       <c r="G36" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>257</v>
+        <v>224</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>258</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>260</v>
+        <v>227</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E37" s="2"/>
-      <c r="F37" s="2" t="s">
-        <v>261</v>
-      </c>
+      <c r="F37" s="2"/>
       <c r="G37" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>262</v>
+        <v>228</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>263</v>
+        <v>229</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>264</v>
+        <v>230</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>265</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>266</v>
+        <v>232</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>267</v>
+        <v>233</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E38" s="2"/>
-      <c r="F38" s="2" t="s">
-        <v>268</v>
-      </c>
+      <c r="F38" s="2"/>
       <c r="G38" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>269</v>
+        <v>234</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>270</v>
+        <v>235</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>272</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>273</v>
+        <v>238</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>274</v>
+        <v>239</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E39" s="2"/>
-      <c r="F39" s="2" t="s">
-        <v>275</v>
-      </c>
+      <c r="F39" s="2"/>
       <c r="G39" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>277</v>
+        <v>241</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>278</v>
+        <v>242</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E40" s="2"/>
-      <c r="F40" s="2" t="s">
-        <v>282</v>
-      </c>
+      <c r="F40" s="2"/>
       <c r="G40" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>283</v>
+        <v>246</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>284</v>
+        <v>247</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>285</v>
+        <v>248</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>286</v>
+        <v>249</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>287</v>
+        <v>250</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>288</v>
+        <v>251</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E41" s="2"/>
-      <c r="F41" s="2" t="s">
-        <v>289</v>
-      </c>
+      <c r="F41" s="2"/>
       <c r="G41" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>290</v>
+        <v>252</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>291</v>
+        <v>253</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>292</v>
+        <v>254</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>293</v>
+        <v>255</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>287</v>
+        <v>250</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>294</v>
+        <v>256</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E42" s="2"/>
-      <c r="F42" s="2" t="s">
-        <v>295</v>
-      </c>
+      <c r="F42" s="2"/>
       <c r="G42" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>296</v>
+        <v>257</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>297</v>
+        <v>258</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>298</v>
+        <v>259</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>299</v>
+        <v>260</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>300</v>
+        <v>261</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>301</v>
+        <v>262</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>302</v>
+        <v>263</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="2" t="s">
-        <v>303</v>
-      </c>
+      <c r="F43" s="2"/>
       <c r="G43" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>304</v>
+        <v>264</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>306</v>
+        <v>266</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>307</v>
+        <v>267</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>308</v>
+        <v>268</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>309</v>
+        <v>269</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>302</v>
+        <v>263</v>
       </c>
       <c r="E44" s="2"/>
-      <c r="F44" s="2" t="s">
-        <v>310</v>
-      </c>
+      <c r="F44" s="2"/>
       <c r="G44" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>311</v>
+        <v>270</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>312</v>
+        <v>271</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>306</v>
+        <v>266</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>307</v>
+        <v>267</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>314</v>
+        <v>273</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>302</v>
+        <v>263</v>
       </c>
       <c r="E45" s="2"/>
-      <c r="F45" s="2" t="s">
-        <v>315</v>
-      </c>
+      <c r="F45" s="2"/>
       <c r="G45" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>316</v>
+        <v>274</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>317</v>
+        <v>275</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>306</v>
+        <v>266</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>307</v>
+        <v>267</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>318</v>
+        <v>276</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>319</v>
+        <v>277</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>320</v>
+        <v>278</v>
       </c>
       <c r="E46" s="2"/>
-      <c r="F46" s="2" t="s">
-        <v>321</v>
-      </c>
+      <c r="F46" s="2"/>
       <c r="G46" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>322</v>
+        <v>279</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>324</v>
+        <v>281</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>325</v>
+        <v>282</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>326</v>
+        <v>283</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>327</v>
+        <v>284</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>320</v>
+        <v>278</v>
       </c>
       <c r="E47" s="2"/>
-      <c r="F47" s="2" t="s">
-        <v>328</v>
-      </c>
+      <c r="F47" s="2"/>
       <c r="G47" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>329</v>
+        <v>285</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>330</v>
+        <v>286</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>331</v>
+        <v>287</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>332</v>
+        <v>288</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>333</v>
+        <v>289</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>320</v>
+        <v>278</v>
       </c>
       <c r="E48" s="2"/>
-      <c r="F48" s="2" t="s">
-        <v>335</v>
-      </c>
+      <c r="F48" s="2"/>
       <c r="G48" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>336</v>
+        <v>291</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>337</v>
+        <v>292</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>338</v>
+        <v>293</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>339</v>
+        <v>294</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>340</v>
+        <v>295</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>341</v>
+        <v>296</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>320</v>
+        <v>278</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="2" t="s">
-        <v>342</v>
-      </c>
+      <c r="F49" s="2"/>
       <c r="G49" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>343</v>
+        <v>297</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>344</v>
+        <v>298</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>345</v>
+        <v>299</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>346</v>
+        <v>300</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>347</v>
+        <v>301</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>348</v>
+        <v>302</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>320</v>
+        <v>278</v>
       </c>
       <c r="E50" s="2"/>
-      <c r="F50" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="F50" s="2"/>
       <c r="G50" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>350</v>
+        <v>303</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>351</v>
+        <v>304</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>352</v>
+        <v>305</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>353</v>
+        <v>306</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>354</v>
+        <v>307</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>355</v>
+        <v>308</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>320</v>
+        <v>278</v>
       </c>
       <c r="E51" s="2"/>
-      <c r="F51" s="2" t="s">
-        <v>356</v>
-      </c>
+      <c r="F51" s="2"/>
       <c r="G51" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>357</v>
+        <v>309</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>358</v>
+        <v>310</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>359</v>
+        <v>311</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>360</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>361</v>
+        <v>313</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>362</v>
+        <v>314</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>320</v>
+        <v>278</v>
       </c>
       <c r="E52" s="2"/>
-      <c r="F52" s="2" t="s">
-        <v>363</v>
-      </c>
+      <c r="F52" s="2"/>
       <c r="G52" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>364</v>
+        <v>315</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>365</v>
+        <v>316</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>366</v>
+        <v>317</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>367</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>368</v>
+        <v>319</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>369</v>
+        <v>320</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>370</v>
+        <v>321</v>
       </c>
       <c r="E53" s="2"/>
-      <c r="F53" s="2" t="s">
-        <v>371</v>
-      </c>
+      <c r="F53" s="2"/>
       <c r="G53" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>372</v>
+        <v>322</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>373</v>
+        <v>323</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>374</v>
+        <v>324</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>299</v>
+        <v>260</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>375</v>
+        <v>325</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>376</v>
+        <v>326</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>370</v>
+        <v>321</v>
       </c>
       <c r="E54" s="2"/>
-      <c r="F54" s="2" t="s">
-        <v>377</v>
-      </c>
+      <c r="F54" s="2"/>
       <c r="G54" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>378</v>
+        <v>327</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>380</v>
+        <v>329</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>381</v>
+        <v>331</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>382</v>
+        <v>332</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>370</v>
+        <v>321</v>
       </c>
       <c r="E55" s="2"/>
-      <c r="F55" s="2" t="s">
-        <v>383</v>
-      </c>
+      <c r="F55" s="2"/>
       <c r="G55" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>384</v>
+        <v>333</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>386</v>
+        <v>335</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>387</v>
+        <v>336</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>388</v>
+        <v>337</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>389</v>
+        <v>338</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>370</v>
+        <v>321</v>
       </c>
       <c r="E56" s="2"/>
-      <c r="F56" s="2" t="s">
-        <v>390</v>
-      </c>
+      <c r="F56" s="2"/>
       <c r="G56" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>391</v>
+        <v>339</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>392</v>
+        <v>340</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>393</v>
+        <v>341</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>394</v>
+        <v>343</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>395</v>
+        <v>344</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>370</v>
+        <v>321</v>
       </c>
       <c r="E57" s="2"/>
-      <c r="F57" s="2" t="s">
-        <v>396</v>
-      </c>
+      <c r="F57" s="2"/>
       <c r="G57" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>397</v>
+        <v>345</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>398</v>
+        <v>346</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>264</v>
+        <v>230</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>265</v>
+        <v>231</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>399</v>
+        <v>347</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>400</v>
+        <v>348</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>370</v>
+        <v>321</v>
       </c>
       <c r="E58" s="2"/>
-      <c r="F58" s="2" t="s">
-        <v>401</v>
-      </c>
+      <c r="F58" s="2"/>
       <c r="G58" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>402</v>
+        <v>349</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>403</v>
+        <v>350</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>404</v>
+        <v>351</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="368">
   <si>
     <t xml:space="preserve">Nombre del producto</t>
   </si>
@@ -34,15 +34,27 @@
     <t xml:space="preserve">Categoría</t>
   </si>
   <si>
-    <t xml:space="preserve">Presentacion</t>
+    <t xml:space="preserve">Presentacion 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presentacion 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presentacion 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio 3</t>
   </si>
   <si>
     <t xml:space="preserve">Descripción</t>
   </si>
   <si>
-    <t xml:space="preserve">Precio</t>
-  </si>
-  <si>
     <t xml:space="preserve">ID imagen</t>
   </si>
   <si>
@@ -148,6 +160,9 @@
     <t xml:space="preserve">DB-LIM-005</t>
   </si>
   <si>
+    <t xml:space="preserve">50 ml</t>
+  </si>
+  <si>
     <t xml:space="preserve">IMG-0005</t>
   </si>
   <si>
@@ -166,6 +181,9 @@
     <t xml:space="preserve">DB-LIM-004</t>
   </si>
   <si>
+    <t xml:space="preserve">120 g</t>
+  </si>
+  <si>
     <t xml:space="preserve">IMG-0004</t>
   </si>
   <si>
@@ -187,6 +205,9 @@
     <t xml:space="preserve">Tratamiento Facial</t>
   </si>
   <si>
+    <t xml:space="preserve">20 g</t>
+  </si>
+  <si>
     <t xml:space="preserve">IMG-0030</t>
   </si>
   <si>
@@ -223,6 +244,9 @@
     <t xml:space="preserve">DB-TRA-005</t>
   </si>
   <si>
+    <t xml:space="preserve">50 g</t>
+  </si>
+  <si>
     <t xml:space="preserve">IMG-0018</t>
   </si>
   <si>
@@ -235,7 +259,7 @@
     <t xml:space="preserve">Ácido Kójico - 1%</t>
   </si>
   <si>
-    <t xml:space="preserve">Crema Hidratante Antiedad Revitalizante Diurna</t>
+    <t xml:space="preserve">Crema Hidratante Antiedad Revitalizante</t>
   </si>
   <si>
     <t xml:space="preserve">DB-TRA-016</t>
@@ -313,6 +337,12 @@
     <t xml:space="preserve">DB-TRA-019</t>
   </si>
   <si>
+    <t xml:space="preserve">100 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80 Pads</t>
+  </si>
+  <si>
     <t xml:space="preserve">IMG-0032</t>
   </si>
   <si>
@@ -343,7 +373,7 @@
     <t xml:space="preserve">Ácido Hialurónico - 1,5%; Centella Asiática - 0,5%; Electrolitos - 90%</t>
   </si>
   <si>
-    <t xml:space="preserve">Parches de Gel para Control de Grasa y Poros con PHA Clear Balance</t>
+    <t xml:space="preserve">Parches de Gel para Control de Grasa y Poros con PHA</t>
   </si>
   <si>
     <t xml:space="preserve">DB-TRA-021</t>
@@ -385,6 +415,9 @@
     <t xml:space="preserve">DB-TRA-008</t>
   </si>
   <si>
+    <t xml:space="preserve">30 g</t>
+  </si>
+  <si>
     <t xml:space="preserve">IMG-0021</t>
   </si>
   <si>
@@ -541,7 +574,7 @@
     <t xml:space="preserve">Retinol Nanosomado - 1%; Ácido Hialurónico - 0,5%</t>
   </si>
   <si>
-    <t xml:space="preserve">After Sun Gel 48h</t>
+    <t xml:space="preserve">After Sun Gel</t>
   </si>
   <si>
     <t xml:space="preserve">DB-COR-002</t>
@@ -550,6 +583,9 @@
     <t xml:space="preserve">Cuidado Corporal</t>
   </si>
   <si>
+    <t xml:space="preserve">160 g</t>
+  </si>
+  <si>
     <t xml:space="preserve">IMG-0054</t>
   </si>
   <si>
@@ -562,12 +598,15 @@
     <t xml:space="preserve">Aloe Vera Extract; Alfa Bisabolol; Camellia Sinensis; Alpha Tocopherol; Agua Termal Dernier</t>
   </si>
   <si>
-    <t xml:space="preserve">Alcohol +70% Solución Esterilizante de Superficies</t>
+    <t xml:space="preserve">Solución Esterilizante de Superficies</t>
   </si>
   <si>
     <t xml:space="preserve">DB-COR-046</t>
   </si>
   <si>
+    <t xml:space="preserve">250 cm3</t>
+  </si>
+  <si>
     <t xml:space="preserve">IMG-0098</t>
   </si>
   <si>
@@ -586,6 +625,9 @@
     <t xml:space="preserve">DB-COR-008</t>
   </si>
   <si>
+    <t xml:space="preserve">90 cm3</t>
+  </si>
+  <si>
     <t xml:space="preserve">IMG-0060</t>
   </si>
   <si>
@@ -628,12 +670,15 @@
     <t xml:space="preserve">Camphor; Menthol; Árnica Montana Flower Extract; Aloe Barbadensis Extract; Fucus Vesiculosus Extract</t>
   </si>
   <si>
-    <t xml:space="preserve">Bronceador SPF 2 (Crema / Spray)</t>
+    <t xml:space="preserve">Bronceador (Crema / Spray)</t>
   </si>
   <si>
     <t xml:space="preserve">DB-COR-001</t>
   </si>
   <si>
+    <t xml:space="preserve">75 g</t>
+  </si>
+  <si>
     <t xml:space="preserve">IMG-0053</t>
   </si>
   <si>
@@ -646,7 +691,7 @@
     <t xml:space="preserve">Tocopheryl Acetate (Vitamina E); Extracto de Zanahoria (Betacaroteno)</t>
   </si>
   <si>
-    <t xml:space="preserve">Enjuague Bucal Placa Bacteriana Sabor Menta</t>
+    <t xml:space="preserve">Enjuague Bucal</t>
   </si>
   <si>
     <t xml:space="preserve">DB-COR-045</t>
@@ -664,7 +709,7 @@
     <t xml:space="preserve">Enjuague bucal contra caries y placa bacteriana sin alcohol sabor a menta fresca.</t>
   </si>
   <si>
-    <t xml:space="preserve">Gel Antibacterial Dernier Skinsept</t>
+    <t xml:space="preserve">Gel Antibacterial</t>
   </si>
   <si>
     <t xml:space="preserve">DB-COR-047</t>
@@ -682,7 +727,7 @@
     <t xml:space="preserve">Alcohol (62%); Cloruro de Benzalcónio; Vitamina E; Aloe Vera</t>
   </si>
   <si>
-    <t xml:space="preserve">Menthol Gel Dol Out (Pre/Post Workout)</t>
+    <t xml:space="preserve">Menthol Gel Dol Out</t>
   </si>
   <si>
     <t xml:space="preserve">DB-COR-005</t>
@@ -790,213 +835,210 @@
     <t xml:space="preserve">Chamomilla Recutita Flower Extract; Aloe Barbadensis Extract; Glicerina</t>
   </si>
   <si>
-    <t xml:space="preserve">DB-INF-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0101.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplique una pequeña cantidad directamente sobre la piel del niño y extienda sobre el área con delicados movimientos circulares, hasta lograr la espuma deseada, luego enjuague con abundante agua.</t>
+    <t xml:space="preserve">CC Stick Luminous Touch 100% Mineral (Tono Dark)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB-MAQ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maquillaje</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0052.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - Gira la base del stick para deslizar el producto hacia arriba. 2 - Aplica directamente sobre el rostro con movimientos suaves desde el centro hacia afuera. Puedes extenderlo también sobre cuello y escote. 3 - Difumina con la brocha integrada hasta lograr un tono y acabado uniforme, natural y sin esfuerzo. Ideal para retoques durante el día gracias a su diseño portátil y práctico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ácido Hialurónico; Cyclopentasiloxane; Zinc Oxide; Extracto de CICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC Stick Luminous Touch 100% Mineral (Tono Light)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB-MAQ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0050.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC Stick Luminous Touch 100% Mineral (Tono Medium)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB-MAQ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0051.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protector Solar Baby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB-SOL-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protección Solar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0046.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tome una generosa porción y aplíquelo 20 minutos antes de exponerse al sol. Para mantener la protección aplique nuevamente en intervalos frecuentes especialmente después de nadar, transpirar o secarse con una toalla.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filtros Minerales Naturales (Dióxido de Titanio y Óxido de Zinc); Aloe Vera Extract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protector Solar en Aerosol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB-SOL-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">195 ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0045.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agitar bien antes de usar. Rocíe 20 minutos antes de la exposición al sol, durante aproximadamente un minuto en cada zona del cuerpo con pulverizaciones cortas a una distancia de 15 centímetros de forma uniforme sobre la piel, incluyendo el dorso de las manos, ingle, interior de las rodillas y pies. Su sistema de válvula aerosol permite una aplicación 360°, desde cualquier ángulo y posición, asegurando una distribución rápida y uniforme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complejo de Filtros UVA/UVB; Aloe Vera Extract; Alfa Bisabolol; Hyaluronic Acid; Alpha Tocopherol; D-Panthenol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protector Solar Facial en Polvo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB-SOL-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0043.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deslizar la brocha de forma generosa y uniforme con movimientos circulares sobre todo el rostro y las zonas expuestas (orejas, cuello, escote y dorso de las manos) para garantizar la correcta liberación de producto. Evite mojar la brocha, ya que el polvo podría humedecerse y perder su efectividad de aplicación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filtros Solares Minerales 100% (Dióxido de Titanio / Óxido de Zinc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protector Solar Facial Gel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB-SOL-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0042.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplique durante la rutina diurna en cantidad suficiente y de manera ascendente sobre la piel de la cara, cuello y escote. Evite el contacto con los ojos. Repita la aplicación varias veces al día para mantener la protección, especialmente después de la sudoración o contacto con el agua. Compatible con el maquillaje, puede ser utilizado justo antes de aplicar la base de maquillaje.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complejo de Filtros UVA/UVB; Matcha Tea Extract; Alfa Bisabolol; D-Panthenol; Hyaluronic Acid; Agua Termal Dernier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protector Solar Facial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB-SOL-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0041.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplique diariamente una capa uniforme en las zonas del cuerpo expuestas como la piel del rostro, cuello y escote, extienda y difumine hasta que se absorba completamente. Puede maquillarse como de costumbre después de la aplicación del Protector Solar Facial FPS 50+.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mezcla de Filtros UV Físicos y Químicos (Dióxido de Titanio); D-Panthenol; Emolientes; Emulsificantes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protector Solar (Crema / Spray)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB-SOL-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0044.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spray: Agite bien antes de usar, rocíe una cantidad generosa de protector y extienda el producto hasta su completa absorción 20 minutos antes de exponerse al sol. Para mantener la protección aplique nuevamente en intervalos frecuentes especialmente después de nadar, transpirar o secarse con una toalla. Crema: Tome una generosa porción y aplíquelo 20 minutos antes de exponerse al sol. Para mantener la protección aplique nuevamente en intervalos frecuentes especialmente después de nadar, transpirar o secarse con una toalla.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mezcla de Filtros UV Físicos y Químicos; Extracto de Aloe Vera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sérum Protector Solar Facial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB-SOL-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0040.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agite antes de usar. Aplique en la mañana 8 gotas sobre el rostro, cuello y escote previamente limpio y seco con un ligero masaje circular ascendente hasta su total absorción, como último paso de la rutina facial, antes del maquillaje. Recuerde reaplicar varias veces al día para mantener la piel protegida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complejo de Filtros UVA/UVB; Complejo de Péptidos - 1%; Colágeno Hidrolizado - 0,20%; Coenzima Q10 - 0,50%; Ácido Hialurónico - 0,10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aceite Cremoso Baby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB-INF-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuidado Infantil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0104.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para aplicar el aceite cremoso en la piel del bebé, primero asegúrate de que la piel esté limpia y seca. Vierte una pequeña cantidad del aceite en tus manos y frótalas para calentarlo ligeramente. Luego, masajes suavemente el aceite sobre la piel del bebé con movimientos circulares, prestando especial atención a las áreas más secas. Este producto es ideal para usar después del baño para ayudar a retener la humedad y mantener la piel suave e hidratada durante 24 horas.</t>
   </si>
   <si>
     <t xml:space="preserve">Aloe Vera; Vitamina E</t>
   </si>
   <si>
-    <t xml:space="preserve">CC Stick Luminous Touch 100% Mineral (Tono Dark)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB-MAQ-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maquillaje</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0052.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - Gira la base del stick para deslizar el producto hacia arriba. 2 - Aplica directamente sobre el rostro con movimientos suaves desde el centro hacia afuera. Puedes extenderlo también sobre cuello y escote. 3 - Difumina con la brocha integrada hasta lograr un tono y acabado uniforme, natural y sin esfuerzo. Ideal para retoques durante el día gracias a su diseño portátil y práctico.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ácido Hialurónico; Cyclopentasiloxane; Zinc Oxide; Extracto de CICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CC Stick Luminous Touch 100% Mineral (Tono Light)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB-MAQ-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0050.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CC Stick Luminous Touch 100% Mineral (Tono Medium)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB-MAQ-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0051.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protector Solar Baby SPF 50+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB-SOL-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protección Solar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0046.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tome una generosa porción y aplíquelo 20 minutos antes de exponerse al sol. Para mantener la protección aplique nuevamente en intervalos frecuentes especialmente después de nadar, transpirar o secarse con una toalla.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filtros Minerales Naturales (Dióxido de Titanio y Óxido de Zinc); Aloe Vera Extract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protector Solar en Aerosol SPF 50+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB-SOL-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0045.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agitar bien antes de usar. Rocíe 20 minutos antes de la exposición al sol, durante aproximadamente un minuto en cada zona del cuerpo con pulverizaciones cortas a una distancia de 15 centímetros de forma uniforme sobre la piel, incluyendo el dorso de las manos, ingle, interior de las rodillas y pies. Su sistema de válvula aerosol permite una aplicación 360°, desde cualquier ángulo y posición, asegurando una distribución rápida y uniforme.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complejo de Filtros UVA/UVB; Aloe Vera Extract; Alfa Bisabolol; Hyaluronic Acid; Alpha Tocopherol; D-Panthenol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protector Solar Facial en Polvo 100% Mineral SPF 45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB-SOL-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0043.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deslizar la brocha de forma generosa y uniforme con movimientos circulares sobre todo el rostro y las zonas expuestas (orejas, cuello, escote y dorso de las manos) para garantizar la correcta liberación de producto. Evite mojar la brocha, ya que el polvo podría humedecerse y perder su efectividad de aplicación.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filtros Solares Minerales 100% (Dióxido de Titanio / Óxido de Zinc)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protector Solar Facial Gel SPF 50+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB-SOL-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0042.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplique durante la rutina diurna en cantidad suficiente y de manera ascendente sobre la piel de la cara, cuello y escote. Evite el contacto con los ojos. Repita la aplicación varias veces al día para mantener la protección, especialmente después de la sudoración o contacto con el agua. Compatible con el maquillaje, puede ser utilizado justo antes de aplicar la base de maquillaje.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complejo de Filtros UVA/UVB; Matcha Tea Extract; Alfa Bisabolol; D-Panthenol; Hyaluronic Acid; Agua Termal Dernier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protector Solar Facial SPF 50+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB-SOL-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0041.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplique diariamente una capa uniforme en las zonas del cuerpo expuestas como la piel del rostro, cuello y escote, extienda y difumine hasta que se absorba completamente. Puede maquillarse como de costumbre después de la aplicación del Protector Solar Facial FPS 50+.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mezcla de Filtros UV Físicos y Químicos (Dióxido de Titanio); D-Panthenol; Emolientes; Emulsificantes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protector Solar SPF 50+ (Crema / Spray)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB-SOL-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0044.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spray: Agite bien antes de usar, rocíe una cantidad generosa de protector y extienda el producto hasta su completa absorción 20 minutos antes de exponerse al sol. Para mantener la protección aplique nuevamente en intervalos frecuentes especialmente después de nadar, transpirar o secarse con una toalla. Crema: Tome una generosa porción y aplíquelo 20 minutos antes de exponerse al sol. Para mantener la protección aplique nuevamente en intervalos frecuentes especialmente después de nadar, transpirar o secarse con una toalla.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mezcla de Filtros UV Físicos y Químicos; Extracto de Aloe Vera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sérum Protector Solar Facial SPF 50+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB-SOL-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0040.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agite antes de usar. Aplique en la mañana 8 gotas sobre el rostro, cuello y escote previamente limpio y seco con un ligero masaje circular ascendente hasta su total absorción, como último paso de la rutina facial, antes del maquillaje. Recuerde reaplicar varias veces al día para mantener la piel protegida.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complejo de Filtros UVA/UVB; Complejo de Péptidos - 1%; Colágeno Hidrolizado - 0,20%; Coenzima Q10 - 0,50%; Ácido Hialurónico - 0,10%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aceite Cremoso Baby 24h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB-INF-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuidado Infantil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0104.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Para aplicar el aceite cremoso en la piel del bebé, primero asegúrate de que la piel esté limpia y seca. Vierte una pequeña cantidad del aceite en tus manos y frótalas para calentarlo ligeramente. Luego, masajes suavemente el aceite sobre la piel del bebé con movimientos circulares, prestando especial atención a las áreas más secas. Este producto es ideal para usar después del baño para ayudar a retener la humedad y mantener la piel suave e hidratada durante 24 horas.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Colonia Baby</t>
   </si>
   <si>
@@ -1021,6 +1063,9 @@
     <t xml:space="preserve">DB-INF-003</t>
   </si>
   <si>
+    <t xml:space="preserve">50 cm3</t>
+  </si>
+  <si>
     <t xml:space="preserve">IMG-0103</t>
   </si>
   <si>
@@ -1033,7 +1078,7 @@
     <t xml:space="preserve">Óxido de Zinc</t>
   </si>
   <si>
-    <t xml:space="preserve">Enjuague Bucal Kids Sabor Cereza</t>
+    <t xml:space="preserve">Enjuague Bucal Kids</t>
   </si>
   <si>
     <t xml:space="preserve">DB-INF-007</t>
@@ -1051,7 +1096,7 @@
     <t xml:space="preserve">Enjuague bucal infantil sin alcohol con sabor a cereza. Protección contra las caries.</t>
   </si>
   <si>
-    <t xml:space="preserve">Repelente de Insectos Baby (Spray / Loción)</t>
+    <t xml:space="preserve">Repelente de Insectos Baby</t>
   </si>
   <si>
     <t xml:space="preserve">DB-INF-006</t>
@@ -1114,7 +1159,6 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1159,7 +1203,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1173,6 +1217,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1299,16 +1347,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:P57"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="43.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="118.44"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="9" min="7" style="0" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="0" width="296.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="115.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="58.75"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="8.76"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="296.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="30.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="18.78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1330,13 +1381,13 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -1345,1776 +1396,2188 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="2" t="s">
         <v>19</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="2" t="s">
         <v>26</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>32</v>
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="2" t="s">
         <v>39</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>45</v>
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>51</v>
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>64</v>
+      <c r="F9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>76</v>
+      <c r="F11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>82</v>
+        <v>60</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>88</v>
+        <v>60</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>94</v>
+        <v>60</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>100</v>
+        <v>60</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="J16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="F16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>106</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>112</v>
+        <v>60</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>118</v>
+        <v>60</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>124</v>
+        <v>60</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>130</v>
+        <v>60</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>136</v>
+      <c r="F21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>142</v>
+        <v>60</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>148</v>
+        <v>60</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>154</v>
+        <v>60</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>160</v>
+        <v>60</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>166</v>
+        <v>60</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>172</v>
+        <v>60</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>179</v>
+        <v>186</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>191</v>
+      <c r="E30" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>201</v>
+        <v>186</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>207</v>
+        <v>26</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>213</v>
+        <v>186</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>219</v>
+        <v>186</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>225</v>
+        <v>186</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>231</v>
+        <v>186</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>237</v>
+        <v>186</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>243</v>
+        <v>186</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>249</v>
+        <v>186</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>255</v>
+        <v>186</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>260</v>
+        <v>273</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>267</v>
+        <v>273</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="O43" s="2"/>
+      <c r="P43" s="2" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>267</v>
+        <v>273</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="O44" s="2"/>
+      <c r="P44" s="2" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>267</v>
+        <v>288</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="O45" s="2"/>
+      <c r="P45" s="2" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="O46" s="2"/>
+      <c r="P46" s="2" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="K47" s="2" t="s">
         <v>288</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="O47" s="2"/>
+      <c r="P47" s="2" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>294</v>
+        <v>288</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="O48" s="2"/>
+      <c r="P48" s="4" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>300</v>
+        <v>288</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="O49" s="2"/>
+      <c r="P49" s="2" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>303</v>
+        <v>288</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>306</v>
+        <v>26</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="O50" s="2"/>
+      <c r="P50" s="2" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>312</v>
+        <v>288</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="O51" s="2"/>
+      <c r="P51" s="2" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>318</v>
+        <v>333</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="O52" s="2"/>
+      <c r="P52" s="2" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>260</v>
+        <v>333</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="O53" s="2"/>
+      <c r="P53" s="2" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" s="2" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H55" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="I55" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>336</v>
+      <c r="E55" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" s="2" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="J56" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>342</v>
+        <v>333</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="J57" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>352</v>
+        <v>333</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" s="2" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -11,9 +11,6 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$O$166</definedName>
-  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -24,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="727">
   <si>
     <t xml:space="preserve">Nombre del producto</t>
   </si>
@@ -1148,6 +1145,9 @@
     <t xml:space="preserve">400ML</t>
   </si>
   <si>
+    <t xml:space="preserve">250ML</t>
+  </si>
+  <si>
     <t xml:space="preserve">Loción corporal con Vitamina E, D-Panthenol, Glicerina y Aloe Vera. Hidratación avanzada antiradicales libres.</t>
   </si>
   <si>
@@ -1161,12 +1161,6 @@
   </si>
   <si>
     <t xml:space="preserve">Vitamina E; D-Panthenol; Glicerina; Aloe Vera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRUCEN ADULTCARE BODY LOTION  250 ML</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250ML</t>
   </si>
   <si>
     <t xml:space="preserve">BRUCEN ADULTCARE CREMA DERMOPROTECTORA ADULTO 100GR</t>
@@ -2303,7 +2297,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2336,7 +2330,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2345,10 +2339,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2447,10 +2437,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2561,15 +2547,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="true">
+  <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W166"/>
+  <dimension ref="A1:W165"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="68.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.33"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8.76"/>
@@ -2629,7 +2615,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="91" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
         <v>15</v>
       </c>
@@ -2666,7 +2652,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="57.45" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>24</v>
       </c>
@@ -2703,7 +2689,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
         <v>30</v>
       </c>
@@ -2740,7 +2726,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
         <v>36</v>
       </c>
@@ -2777,7 +2763,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="57.45" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
         <v>43</v>
       </c>
@@ -2812,7 +2798,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
         <v>49</v>
       </c>
@@ -2849,7 +2835,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="68.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
         <v>55</v>
       </c>
@@ -2886,7 +2872,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>61</v>
       </c>
@@ -2923,7 +2909,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
         <v>68</v>
       </c>
@@ -2960,7 +2946,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
         <v>75</v>
       </c>
@@ -2998,7 +2984,7 @@
       </c>
       <c r="U11" s="8"/>
     </row>
-    <row r="12" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
         <v>82</v>
       </c>
@@ -3035,7 +3021,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="68.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
         <v>88</v>
       </c>
@@ -3072,7 +3058,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="57.45" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
         <v>94</v>
       </c>
@@ -3110,7 +3096,7 @@
       </c>
       <c r="Q14" s="8"/>
     </row>
-    <row r="15" customFormat="false" ht="57.45" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
         <v>100</v>
       </c>
@@ -3148,7 +3134,7 @@
       </c>
       <c r="R15" s="8"/>
     </row>
-    <row r="16" customFormat="false" ht="35.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
         <v>106</v>
       </c>
@@ -3186,7 +3172,7 @@
       </c>
       <c r="R16" s="8"/>
     </row>
-    <row r="17" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
         <v>112</v>
       </c>
@@ -3224,7 +3210,7 @@
       </c>
       <c r="W17" s="8"/>
     </row>
-    <row r="18" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
         <v>118</v>
       </c>
@@ -3261,7 +3247,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
         <v>124</v>
       </c>
@@ -3299,7 +3285,7 @@
       </c>
       <c r="R19" s="8"/>
     </row>
-    <row r="20" customFormat="false" ht="57.45" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
         <v>130</v>
       </c>
@@ -3337,7 +3323,7 @@
       </c>
       <c r="Q20" s="8"/>
     </row>
-    <row r="21" customFormat="false" ht="68.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
         <v>136</v>
       </c>
@@ -3375,7 +3361,7 @@
       </c>
       <c r="T21" s="8"/>
     </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
         <v>142</v>
       </c>
@@ -3413,7 +3399,7 @@
       </c>
       <c r="V22" s="8"/>
     </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
         <v>148</v>
       </c>
@@ -3450,7 +3436,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="35.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
         <v>148</v>
       </c>
@@ -3487,7 +3473,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
         <v>155</v>
       </c>
@@ -3524,7 +3510,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
         <v>161</v>
       </c>
@@ -3561,7 +3547,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
         <v>165</v>
       </c>
@@ -3598,7 +3584,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
         <v>169</v>
       </c>
@@ -3635,7 +3621,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
         <v>175</v>
       </c>
@@ -3672,7 +3658,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
         <v>182</v>
       </c>
@@ -3709,7 +3695,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
         <v>183</v>
       </c>
@@ -3746,7 +3732,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
         <v>184</v>
       </c>
@@ -3783,7 +3769,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="57.45" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
         <v>185</v>
       </c>
@@ -3820,7 +3806,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="68.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
         <v>192</v>
       </c>
@@ -3857,7 +3843,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="68.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
         <v>198</v>
       </c>
@@ -3894,7 +3880,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="68.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
         <v>198</v>
       </c>
@@ -4223,7 +4209,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="35.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
         <v>237</v>
       </c>
@@ -4260,7 +4246,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="35.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
         <v>237</v>
       </c>
@@ -4297,7 +4283,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
         <v>246</v>
       </c>
@@ -4332,7 +4318,7 @@
       </c>
       <c r="O47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="35.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
         <v>253</v>
       </c>
@@ -4369,7 +4355,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
         <v>259</v>
       </c>
@@ -4396,7 +4382,7 @@
       <c r="N49" s="5"/>
       <c r="O49" s="3"/>
     </row>
-    <row r="50" customFormat="false" ht="57.45" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
         <v>230</v>
       </c>
@@ -4433,7 +4419,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="57.45" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
         <v>236</v>
       </c>
@@ -4470,7 +4456,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="57.45" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="s">
         <v>263</v>
       </c>
@@ -4507,7 +4493,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="35.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="s">
         <v>271</v>
       </c>
@@ -4544,7 +4530,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="35.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="s">
         <v>277</v>
       </c>
@@ -4581,14 +4567,14 @@
         <v>283</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="35.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="s">
         <v>284</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="0" t="s">
+      <c r="D55" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E55" s="1" t="s">
@@ -4613,14 +4599,14 @@
         <v>283</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="9" t="s">
         <v>288</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D56" s="0" t="s">
+      <c r="D56" s="1" t="s">
         <v>247</v>
       </c>
       <c r="E56" s="1" t="s">
@@ -4642,14 +4628,14 @@
         <v>292</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="35.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="s">
         <v>293</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D57" s="0" t="s">
+      <c r="D57" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E57" s="1" t="s">
@@ -4674,14 +4660,14 @@
         <v>299</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="57.45" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
         <v>300</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D58" s="0" t="s">
+      <c r="D58" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E58" s="1" t="s">
@@ -4706,14 +4692,14 @@
         <v>305</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="113.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
         <v>306</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D59" s="0" t="s">
+      <c r="D59" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E59" s="1" t="s">
@@ -4738,14 +4724,14 @@
         <v>311</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="68.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
         <v>312</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D60" s="0" t="s">
+      <c r="D60" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E60" s="1" t="s">
@@ -4770,14 +4756,14 @@
         <v>317</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="102.2" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
         <v>318</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D61" s="0" t="s">
+      <c r="D61" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E61" s="1" t="s">
@@ -4802,14 +4788,14 @@
         <v>323</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="35.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
         <v>324</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D62" s="0" t="s">
+      <c r="D62" s="1" t="s">
         <v>238</v>
       </c>
       <c r="E62" s="1" t="s">
@@ -4834,14 +4820,14 @@
         <v>244</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="35.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
         <v>325</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D63" s="0" t="s">
+      <c r="D63" s="1" t="s">
         <v>238</v>
       </c>
       <c r="E63" s="1" t="s">
@@ -4866,14 +4852,14 @@
         <v>244</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
         <v>326</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D64" s="0" t="s">
+      <c r="D64" s="1" t="s">
         <v>327</v>
       </c>
       <c r="E64" s="1" t="s">
@@ -4898,14 +4884,14 @@
         <v>160</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>329</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D65" s="0" t="s">
+      <c r="D65" s="1" t="s">
         <v>327</v>
       </c>
       <c r="E65" s="1" t="s">
@@ -4930,14 +4916,14 @@
         <v>160</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="46.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
         <v>330</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D66" s="0" t="s">
+      <c r="D66" s="1" t="s">
         <v>327</v>
       </c>
       <c r="E66" s="1" t="s">
@@ -4962,14 +4948,14 @@
         <v>160</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="35.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
         <v>331</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D67" s="0" t="s">
+      <c r="D67" s="1" t="s">
         <v>327</v>
       </c>
       <c r="E67" s="1" t="s">
@@ -4994,14 +4980,14 @@
         <v>337</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="23.85" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
         <v>338</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D68" s="0" t="s">
+      <c r="D68" s="1" t="s">
         <v>327</v>
       </c>
       <c r="E68" s="1" t="s">
@@ -5026,14 +5012,14 @@
         <v>343</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="23.85" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
         <v>344</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D69" s="0" t="s">
+      <c r="D69" s="1" t="s">
         <v>327</v>
       </c>
       <c r="E69" s="1" t="s">
@@ -5058,14 +5044,14 @@
         <v>349</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="35.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
         <v>350</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D70" s="0" t="s">
+      <c r="D70" s="1" t="s">
         <v>327</v>
       </c>
       <c r="E70" s="1" t="s">
@@ -5090,14 +5076,14 @@
         <v>356</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
         <v>357</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D71" s="0" t="s">
+      <c r="D71" s="1" t="s">
         <v>327</v>
       </c>
       <c r="E71" s="1" t="s">
@@ -5107,14 +5093,14 @@
         <v>6.82666666666667</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
         <v>359</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D72" s="0" t="s">
+      <c r="D72" s="1" t="s">
         <v>327</v>
       </c>
       <c r="E72" s="1" t="s">
@@ -5124,14 +5110,14 @@
         <v>8.69333333333333</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>360</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D73" s="0" t="s">
+      <c r="D73" s="1" t="s">
         <v>327</v>
       </c>
       <c r="E73" s="1" t="s">
@@ -5141,14 +5127,14 @@
         <v>12.4133333333333</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
         <v>361</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D74" s="0" t="s">
+      <c r="D74" s="1" t="s">
         <v>327</v>
       </c>
       <c r="E74" s="1" t="s">
@@ -5158,14 +5144,14 @@
         <v>6.85333333333333</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
         <v>362</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D75" s="0" t="s">
+      <c r="D75" s="1" t="s">
         <v>327</v>
       </c>
       <c r="E75" s="1" t="s">
@@ -5175,14 +5161,14 @@
         <v>6.85333333333333</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
         <v>363</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D76" s="0" t="s">
+      <c r="D76" s="1" t="s">
         <v>327</v>
       </c>
       <c r="E76" s="1" t="s">
@@ -5192,14 +5178,14 @@
         <v>6.85333333333333</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
         <v>364</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D77" s="0" t="s">
+      <c r="D77" s="1" t="s">
         <v>327</v>
       </c>
       <c r="E77" s="1" t="s">
@@ -5209,14 +5195,14 @@
         <v>6.85333333333333</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
         <v>365</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D78" s="0" t="s">
+      <c r="D78" s="1" t="s">
         <v>366</v>
       </c>
       <c r="E78" s="1" t="s">
@@ -5226,14 +5212,14 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
         <v>367</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D79" s="0" t="s">
+      <c r="D79" s="1" t="s">
         <v>366</v>
       </c>
       <c r="E79" s="1" t="s">
@@ -5243,14 +5229,14 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
         <v>368</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D80" s="0" t="s">
+      <c r="D80" s="1" t="s">
         <v>366</v>
       </c>
       <c r="E80" s="1" t="s">
@@ -5260,14 +5246,14 @@
         <v>3.53333333333333</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="23.85" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B81" s="0" t="s">
+      <c r="B81" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D81" s="0" t="s">
+      <c r="D81" s="1" t="s">
         <v>372</v>
       </c>
       <c r="E81" s="1" t="s">
@@ -5276,222 +5262,225 @@
       <c r="F81" s="10" t="n">
         <v>13.32</v>
       </c>
+      <c r="G81" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="H81" s="10" t="n">
+        <v>9.36</v>
+      </c>
       <c r="K81" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="23.85" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="B82" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D82" s="0" t="s">
+      <c r="D82" s="1" t="s">
         <v>372</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>9.36</v>
+        <v>7.20583244619216</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="N82" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="B83" s="0" t="s">
+        <v>386</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D83" s="0" t="s">
+      <c r="D83" s="1" t="s">
         <v>372</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F83" s="10" t="n">
-        <v>7.20583244619216</v>
+        <v>7.12887282217288</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="B84" s="0" t="s">
+        <v>392</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D84" s="0" t="s">
-        <v>372</v>
+      <c r="D84" s="1" t="s">
+        <v>393</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>388</v>
+        <v>239</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>7.12887282217288</v>
+        <v>9.41425446816473</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B85" s="0" t="s">
+      <c r="E85" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="F85" s="10" t="n">
+        <v>16.1425471275276</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="O85" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D85" s="0" t="s">
-        <v>394</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F85" s="10" t="n">
-        <v>9.41425446816473</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="L85" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="M85" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="O85" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="B86" s="0" t="s">
+      <c r="D86" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="F86" s="10" t="n">
+        <v>8.17421149404765</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="O86" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D86" s="0" t="s">
-        <v>394</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="F86" s="10" t="n">
-        <v>16.1425471275276</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="M86" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="O86" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="B87" s="0" t="s">
-        <v>371</v>
-      </c>
-      <c r="D87" s="0" t="s">
-        <v>394</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>405</v>
+      <c r="D87" s="1" t="s">
+        <v>393</v>
       </c>
       <c r="F87" s="10" t="n">
-        <v>8.17421149404765</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="L87" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="M87" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="O87" s="1" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>47.5739038023044</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B88" s="0" t="s">
+      <c r="B88" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D88" s="0" t="s">
-        <v>394</v>
+      <c r="D88" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>369</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>47.5739038023044</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>4.43564063414339</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="O88" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="B89" s="0" t="s">
+        <v>415</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D89" s="0" t="s">
-        <v>394</v>
+      <c r="D89" s="1" t="s">
+        <v>393</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>369</v>
@@ -5500,2190 +5489,2068 @@
         <v>4.43564063414339</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="B90" s="0" t="s">
+        <v>420</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D90" s="0" t="s">
-        <v>394</v>
+      <c r="D90" s="1" t="s">
+        <v>421</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>369</v>
+        <v>422</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>4.43564063414339</v>
+        <v>9.10322409828036</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B91" s="0" t="s">
+      <c r="E91" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="F91" s="10" t="n">
+        <v>8.69874275637259</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="M91" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="O91" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D91" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="F91" s="10" t="n">
-        <v>9.10322409828036</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="L91" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="M91" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="O91" s="1" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="B92" s="0" t="s">
+      <c r="D92" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F92" s="10" t="n">
+        <v>6.1526914161219</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="O92" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D92" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="F92" s="10" t="n">
-        <v>8.69874275637259</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="L92" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="M92" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="O92" s="1" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="B93" s="0" t="s">
+      <c r="D93" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="F93" s="10" t="n">
+        <v>12.8384257580547</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="O93" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D93" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="F93" s="10" t="n">
-        <v>6.1526914161219</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="L93" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="M93" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="O93" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="s">
+      <c r="D94" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B94" s="0" t="s">
-        <v>371</v>
-      </c>
-      <c r="D94" s="0" t="s">
+      <c r="E94" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>9.9453468044268</v>
+      </c>
+      <c r="K94" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="E94" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="F94" s="10" t="n">
-        <v>12.8384257580547</v>
-      </c>
-      <c r="K94" s="1" t="s">
+      <c r="L94" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="L94" s="1" t="s">
+      <c r="M94" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="M94" s="1" t="s">
+      <c r="O94" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="O94" s="1" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B95" s="0" t="s">
+      <c r="B95" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D95" s="0" t="s">
-        <v>440</v>
+      <c r="D95" s="1" t="s">
+        <v>439</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>380</v>
+        <v>446</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>9.9453468044268</v>
+        <v>10.0912863679472</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="B96" s="0" t="s">
+        <v>450</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D96" s="0" t="s">
-        <v>440</v>
+      <c r="D96" s="1" t="s">
+        <v>439</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>447</v>
+        <v>239</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>10.0912863679472</v>
+        <v>21.7676927338399</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="B97" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D97" s="0" t="s">
-        <v>440</v>
+      <c r="D97" s="1" t="s">
+        <v>439</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>239</v>
+        <v>456</v>
       </c>
       <c r="F97" s="10" t="n">
-        <v>21.7676927338399</v>
+        <v>11.2449714229459</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="B98" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D98" s="0" t="s">
-        <v>440</v>
+      <c r="D98" s="1" t="s">
+        <v>439</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>11.2449714229459</v>
+        <v>4.3868758954215</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="M98" s="1" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="B99" s="0" t="s">
-        <v>371</v>
-      </c>
-      <c r="D99" s="0" t="s">
-        <v>440</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>463</v>
       </c>
       <c r="F99" s="10" t="n">
         <v>4.3868758954215</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="B100" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D100" s="0" t="s">
-        <v>440</v>
+      <c r="D100" s="1" t="s">
+        <v>439</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F100" s="10" t="n">
         <v>4.3868758954215</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="M100" s="1" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="B101" s="0" t="s">
+        <v>477</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D101" s="0" t="s">
-        <v>440</v>
+      <c r="D101" s="1" t="s">
+        <v>478</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>4.3868758954215</v>
+        <v>4.39</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="M101" s="1" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="O101" s="1" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="B102" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D102" s="0" t="s">
-        <v>479</v>
+      <c r="D102" s="1" t="s">
+        <v>484</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>463</v>
+        <v>374</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>4.39</v>
+        <v>3.15658586904879</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="M102" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="O102" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B103" s="0" t="s">
-        <v>371</v>
-      </c>
-      <c r="D103" s="0" t="s">
-        <v>485</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="F103" s="10" t="n">
         <v>3.15658586904879</v>
       </c>
       <c r="K103" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="L103" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="L103" s="1" t="s">
+      <c r="M103" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="M103" s="1" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B104" s="0" t="s">
+      <c r="B104" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D104" s="0" t="s">
-        <v>485</v>
+      <c r="D104" s="1" t="s">
+        <v>484</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="F104" s="10" t="n">
         <v>3.15658586904879</v>
       </c>
       <c r="K104" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="L104" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="L104" s="1" t="s">
+      <c r="M104" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="M104" s="1" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B105" s="0" t="s">
+      <c r="B105" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D105" s="0" t="s">
-        <v>485</v>
+      <c r="D105" s="1" t="s">
+        <v>491</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>380</v>
+        <v>239</v>
       </c>
       <c r="F105" s="10" t="n">
-        <v>3.15658586904879</v>
+        <v>6.96608725800308</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="M105" s="1" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>494</v>
+      </c>
+      <c r="O105" s="1" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="B106" s="0" t="s">
-        <v>371</v>
-      </c>
-      <c r="D106" s="0" t="s">
-        <v>492</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>239</v>
+        <v>404</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>6.96608725800308</v>
-      </c>
-      <c r="K106" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="L106" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="M106" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="O106" s="1" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>13.6358622308997</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="B107" s="0" t="s">
+      <c r="B107" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D107" s="0" t="s">
-        <v>492</v>
+      <c r="D107" s="1" t="s">
+        <v>491</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>405</v>
+        <v>351</v>
       </c>
       <c r="F107" s="10" t="n">
-        <v>13.6358622308997</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>8.42424160894899</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="M107" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="O107" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="B108" s="0" t="s">
+        <v>501</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D108" s="0" t="s">
-        <v>492</v>
+      <c r="D108" s="1" t="s">
+        <v>491</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>351</v>
+        <v>404</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>8.42424160894899</v>
+        <v>7.60694458797006</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="M108" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="O108" s="1" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="B109" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D109" s="0" t="s">
-        <v>492</v>
+      <c r="D109" s="1" t="s">
+        <v>491</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F109" s="10" t="n">
-        <v>7.60694458797006</v>
+        <v>9.74337212295685</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="M109" s="1" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="O109" s="1" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="B110" s="0" t="s">
+        <v>511</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D110" s="0" t="s">
-        <v>492</v>
+      <c r="D110" s="1" t="s">
+        <v>512</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>9.74337212295685</v>
+        <v>14.0873350483031</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="M110" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="O110" s="1" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B111" s="0" t="s">
+      <c r="E111" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="F111" s="10" t="n">
+        <v>10.1019259473047</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="L111" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="M111" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="O111" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D111" s="0" t="s">
-        <v>513</v>
-      </c>
-      <c r="E111" s="1" t="s">
+      <c r="D112" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="F112" s="10" t="n">
+        <v>11.4703531790024</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="M112" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="O112" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="F111" s="10" t="n">
-        <v>14.0873350483031</v>
-      </c>
-      <c r="K111" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="L111" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="M111" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="O111" s="1" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="B112" s="0" t="s">
+      <c r="F113" s="10" t="n">
+        <v>15.3202849695152</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="L113" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="M113" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="O113" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D112" s="0" t="s">
-        <v>513</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="F112" s="10" t="n">
-        <v>10.1019259473047</v>
-      </c>
-      <c r="K112" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="L112" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="M112" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="O112" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="B113" s="0" t="s">
-        <v>371</v>
-      </c>
-      <c r="D113" s="0" t="s">
-        <v>513</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="F113" s="10" t="n">
-        <v>11.4703531790024</v>
-      </c>
-      <c r="K113" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="L113" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="M113" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="O113" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="B114" s="0" t="s">
-        <v>371</v>
-      </c>
-      <c r="D114" s="0" t="s">
-        <v>513</v>
+      <c r="D114" s="1" t="s">
+        <v>532</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>373</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>15.3202849695152</v>
-      </c>
-      <c r="K114" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="L114" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="M114" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="O114" s="1" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>15.3663898133977</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="B115" s="0" t="s">
+      <c r="E115" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="F115" s="10" t="n">
+        <v>10.5750325760684</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D115" s="0" t="s">
-        <v>533</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="F115" s="10" t="n">
-        <v>15.3663898133977</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="B116" s="0" t="s">
-        <v>371</v>
-      </c>
-      <c r="D116" s="0" t="s">
-        <v>533</v>
+      <c r="D116" s="1" t="s">
+        <v>532</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>535</v>
+        <v>374</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>10.5750325760684</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>8.68828050333771</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="B117" s="0" t="s">
+      <c r="B117" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D117" s="0" t="s">
-        <v>533</v>
+      <c r="D117" s="1" t="s">
+        <v>532</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="F117" s="10" t="n">
-        <v>8.68828050333771</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6.43907342716138</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="B118" s="0" t="s">
+      <c r="B118" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D118" s="0" t="s">
-        <v>533</v>
+      <c r="D118" s="1" t="s">
+        <v>538</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>405</v>
+        <v>539</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>6.43907342716138</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9.73681104901972</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="B119" s="0" t="s">
-        <v>371</v>
-      </c>
-      <c r="D119" s="0" t="s">
-        <v>539</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>540</v>
+        <v>446</v>
       </c>
       <c r="F119" s="10" t="n">
-        <v>9.73681104901972</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>8.88404876351578</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="B120" s="0" t="s">
-        <v>371</v>
-      </c>
-      <c r="D120" s="0" t="s">
-        <v>539</v>
+      <c r="B120" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>542</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>447</v>
+        <v>543</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>8.88404876351578</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2.92</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="L120" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="M120" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="O120" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="B121" s="0" t="s">
+      <c r="D121" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="F121" s="10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="M121" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="O121" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="D121" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="F121" s="10" t="n">
+      <c r="F122" s="10" t="n">
         <v>2.92</v>
       </c>
-      <c r="K121" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="L121" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M121" s="1" t="s">
+      <c r="K122" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="M122" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="O122" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="O121" s="1" t="s">
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="E123" s="1" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="122" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="1" t="s">
+      <c r="F123" s="10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="L123" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="M123" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="O123" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="B122" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="D122" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="F122" s="10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="L122" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M122" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="O122" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="B123" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="D123" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="F123" s="10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K123" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="L123" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="M123" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="O123" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="B124" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="D124" s="0" t="s">
-        <v>543</v>
+      <c r="D124" s="1" t="s">
+        <v>542</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1.97</v>
+        <v>4.52562911343399</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="M124" s="1" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="O124" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="B125" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="D125" s="0" t="s">
-        <v>543</v>
+        <v>559</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>542</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>555</v>
+        <v>404</v>
       </c>
       <c r="F125" s="10" t="n">
-        <v>4.52562911343399</v>
+        <v>4.63</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="M125" s="1" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="O125" s="1" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="B126" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="D126" s="0" t="s">
-        <v>543</v>
+        <v>564</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>542</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>405</v>
+        <v>462</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>4.63</v>
+        <v>4.57</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="M126" s="1" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="O126" s="1" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="B127" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="D127" s="0" t="s">
-        <v>543</v>
+        <v>569</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>542</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>463</v>
+        <v>570</v>
       </c>
       <c r="F127" s="10" t="n">
-        <v>4.57</v>
+        <v>7.11</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="M127" s="1" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="O127" s="1" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="E128" s="1" t="s">
         <v>570</v>
-      </c>
-      <c r="B128" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="D128" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>571</v>
       </c>
       <c r="F128" s="10" t="n">
         <v>7.11</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="M128" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="O128" s="1" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="B129" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="D129" s="0" t="s">
-        <v>543</v>
+        <v>580</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>581</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="F129" s="10" t="n">
-        <v>7.11</v>
+        <v>3.89</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="M129" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="O129" s="1" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="B130" s="0" t="s">
+        <v>586</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E130" s="1" t="s">
         <v>582</v>
-      </c>
-      <c r="D130" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>583</v>
       </c>
       <c r="F130" s="10" t="n">
         <v>3.89</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="M130" s="1" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="B131" s="0" t="s">
+        <v>590</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E131" s="1" t="s">
         <v>582</v>
-      </c>
-      <c r="D131" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>583</v>
       </c>
       <c r="F131" s="10" t="n">
         <v>3.89</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="M131" s="1" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="B132" s="0" t="s">
+        <v>594</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>582</v>
-      </c>
-      <c r="D132" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>583</v>
       </c>
       <c r="F132" s="10" t="n">
         <v>3.89</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="M132" s="1" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="B133" s="0" t="s">
+      <c r="B133" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>582</v>
-      </c>
-      <c r="D133" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>583</v>
       </c>
       <c r="F133" s="10" t="n">
         <v>3.89</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="M133" s="1" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="B134" s="0" t="s">
+      <c r="B134" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E134" s="1" t="s">
         <v>582</v>
-      </c>
-      <c r="D134" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>583</v>
       </c>
       <c r="F134" s="10" t="n">
         <v>3.89</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="M134" s="1" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="B135" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D135" s="0" t="s">
-        <v>582</v>
+      <c r="B135" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>581</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>583</v>
+        <v>598</v>
       </c>
       <c r="F135" s="10" t="n">
-        <v>3.89</v>
+        <v>5.33</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="136" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>601</v>
+      </c>
+      <c r="O135" s="1" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>598</v>
-      </c>
-      <c r="B136" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D136" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>599</v>
       </c>
       <c r="F136" s="10" t="n">
         <v>5.33</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="O136" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="B137" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D137" s="0" t="s">
-        <v>582</v>
+        <v>608</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>581</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F137" s="10" t="n">
         <v>5.33</v>
       </c>
       <c r="K137" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="M137" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="O137" s="1" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="B138" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D138" s="0" t="s">
-        <v>582</v>
+        <v>612</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>581</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F138" s="10" t="n">
         <v>5.33</v>
       </c>
       <c r="K138" s="1" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="M138" s="1" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>601</v>
+      </c>
+      <c r="O138" s="1" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="B139" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D139" s="0" t="s">
-        <v>582</v>
+      <c r="B139" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>581</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>599</v>
+        <v>614</v>
       </c>
       <c r="F139" s="10" t="n">
-        <v>5.33</v>
+        <v>3.33</v>
       </c>
       <c r="K139" s="1" t="s">
-        <v>600</v>
+        <v>615</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>601</v>
+        <v>616</v>
       </c>
       <c r="M139" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="O139" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E140" s="1" t="s">
         <v>614</v>
-      </c>
-      <c r="B140" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D140" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>615</v>
       </c>
       <c r="F140" s="10" t="n">
         <v>3.33</v>
       </c>
       <c r="K140" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="M140" s="1" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="B141" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D141" s="0" t="s">
-        <v>582</v>
+        <v>622</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>581</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F141" s="10" t="n">
         <v>3.33</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="M141" s="1" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="142" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="B142" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D142" s="0" t="s">
-        <v>582</v>
+        <v>626</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>581</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>3.33</v>
+        <v>16.67</v>
       </c>
       <c r="K142" s="1" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="M142" s="1" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>630</v>
+      </c>
+      <c r="O142" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="B143" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D143" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="F143" s="10" t="n">
-        <v>16.67</v>
+        <v>30</v>
       </c>
       <c r="K143" s="1" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="M143" s="1" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="B144" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D144" s="0" t="s">
-        <v>582</v>
+        <v>637</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>581</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>628</v>
+        <v>638</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="K144" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="L144" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="M144" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="O144" s="1" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10.56</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="B145" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D145" s="0" t="s">
-        <v>582</v>
+        <v>639</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>581</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>639</v>
+        <v>446</v>
       </c>
       <c r="F145" s="10" t="n">
-        <v>10.56</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>13.33</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="B146" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D146" s="0" t="s">
-        <v>582</v>
+      <c r="B146" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>581</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>13.33</v>
-      </c>
-    </row>
-    <row r="147" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7.78</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="B147" s="0" t="s">
+      <c r="B147" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E147" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="D147" s="0" t="s">
+      <c r="F147" s="10" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K147" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="L147" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="M147" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="N147" s="1"/>
+      <c r="O147" s="1" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="E147" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="F147" s="10" t="n">
-        <v>7.78</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="0" t="s">
-        <v>642</v>
-      </c>
-      <c r="B148" s="0" t="s">
+      <c r="F148" s="10" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K148" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="L148" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="M148" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="N148" s="1"/>
+      <c r="O148" s="1" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E149" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="D148" s="0" t="s">
+      <c r="F149" s="10" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K149" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="L149" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="M149" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="N149" s="1"/>
+      <c r="O149" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E150" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="E148" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="F148" s="11" t="n">
+      <c r="F150" s="10" t="n">
         <v>3.89</v>
       </c>
-      <c r="G148" s="0"/>
-      <c r="H148" s="0"/>
-      <c r="I148" s="0"/>
-      <c r="J148" s="0"/>
-      <c r="K148" s="0" t="s">
-        <v>643</v>
-      </c>
-      <c r="L148" s="0" t="s">
-        <v>644</v>
-      </c>
-      <c r="M148" s="0" t="s">
-        <v>645</v>
-      </c>
-      <c r="N148" s="0"/>
-      <c r="O148" s="0" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="0" t="s">
-        <v>647</v>
-      </c>
-      <c r="B149" s="0" t="s">
+      <c r="K150" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="L150" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="M150" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="N150" s="1"/>
+      <c r="O150" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E151" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="D149" s="0" t="s">
+      <c r="F151" s="10" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K151" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="L151" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="M151" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="N151" s="1"/>
+      <c r="O151" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E152" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="E149" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="F149" s="11" t="n">
+      <c r="F152" s="10" t="n">
         <v>3.89</v>
       </c>
-      <c r="G149" s="0"/>
-      <c r="H149" s="0"/>
-      <c r="I149" s="0"/>
-      <c r="J149" s="0"/>
-      <c r="K149" s="0" t="s">
-        <v>648</v>
-      </c>
-      <c r="L149" s="0" t="s">
-        <v>649</v>
-      </c>
-      <c r="M149" s="0" t="s">
-        <v>650</v>
-      </c>
-      <c r="N149" s="0"/>
-      <c r="O149" s="0" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="150" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="0" t="s">
-        <v>652</v>
-      </c>
-      <c r="B150" s="0" t="s">
+      <c r="K152" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="L152" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="M152" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="N152" s="1"/>
+      <c r="O152" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="D150" s="0" t="s">
+      <c r="F153" s="10" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K153" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="L153" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="M153" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="N153" s="1"/>
+      <c r="O153" s="1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E154" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="E150" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="F150" s="11" t="n">
+      <c r="F154" s="10" t="n">
         <v>3.89</v>
       </c>
-      <c r="G150" s="0"/>
-      <c r="H150" s="0"/>
-      <c r="I150" s="0"/>
-      <c r="J150" s="0"/>
-      <c r="K150" s="0" t="s">
-        <v>653</v>
-      </c>
-      <c r="L150" s="0" t="s">
-        <v>654</v>
-      </c>
-      <c r="M150" s="0" t="s">
-        <v>655</v>
-      </c>
-      <c r="N150" s="0"/>
-      <c r="O150" s="0" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="151" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="0" t="s">
-        <v>657</v>
-      </c>
-      <c r="B151" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D151" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E151" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="F151" s="11" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="G151" s="0"/>
-      <c r="H151" s="0"/>
-      <c r="I151" s="0"/>
-      <c r="J151" s="0"/>
-      <c r="K151" s="0" t="s">
-        <v>658</v>
-      </c>
-      <c r="L151" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="M151" s="0" t="s">
-        <v>660</v>
-      </c>
-      <c r="N151" s="0"/>
-      <c r="O151" s="0" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="0" t="s">
-        <v>662</v>
-      </c>
-      <c r="B152" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D152" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E152" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="F152" s="11" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="G152" s="0"/>
-      <c r="H152" s="0"/>
-      <c r="I152" s="0"/>
-      <c r="J152" s="0"/>
-      <c r="K152" s="0" t="s">
-        <v>663</v>
-      </c>
-      <c r="L152" s="0" t="s">
-        <v>664</v>
-      </c>
-      <c r="M152" s="0" t="s">
-        <v>665</v>
-      </c>
-      <c r="N152" s="0"/>
-      <c r="O152" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="0" t="s">
+      <c r="K154" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="L154" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="M154" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="N154" s="1"/>
+      <c r="O154" s="1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="F155" s="10" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="K155" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="L155" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="M155" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="N155" s="1"/>
+      <c r="O155" s="1" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F156" s="10" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="K156" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="L156" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="M156" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="N156" s="1"/>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F157" s="10" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="K157" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="L157" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="M157" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="N157" s="1"/>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="F158" s="10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K158" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="L158" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="M158" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="N158" s="1"/>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="F159" s="10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K159" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="L159" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="M159" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="N159" s="1"/>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="F160" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K160" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="L160" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="M160" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="N160" s="1"/>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="F161" s="10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K161" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="L161" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="M161" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="N161" s="1"/>
+      <c r="O161" s="1" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="F162" s="10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K162" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="L162" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="M162" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="N162" s="1"/>
+      <c r="O162" s="1" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="F163" s="10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K163" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="B153" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D153" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E153" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="F153" s="11" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="G153" s="0"/>
-      <c r="H153" s="0"/>
-      <c r="I153" s="0"/>
-      <c r="J153" s="0"/>
-      <c r="K153" s="0" t="s">
+      <c r="L163" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="L153" s="0" t="s">
+      <c r="M163" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="M153" s="0" t="s">
+      <c r="N163" s="1"/>
+      <c r="O163" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="N153" s="0"/>
-      <c r="O153" s="0" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="0" t="s">
-        <v>672</v>
-      </c>
-      <c r="B154" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D154" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E154" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="F154" s="11" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="G154" s="0"/>
-      <c r="H154" s="0"/>
-      <c r="I154" s="0"/>
-      <c r="J154" s="0"/>
-      <c r="K154" s="0" t="s">
-        <v>673</v>
-      </c>
-      <c r="L154" s="0" t="s">
-        <v>674</v>
-      </c>
-      <c r="M154" s="0" t="s">
-        <v>675</v>
-      </c>
-      <c r="N154" s="0"/>
-      <c r="O154" s="0" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="0" t="s">
-        <v>677</v>
-      </c>
-      <c r="B155" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D155" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E155" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="F155" s="11" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="G155" s="0"/>
-      <c r="H155" s="0"/>
-      <c r="I155" s="0"/>
-      <c r="J155" s="0"/>
-      <c r="K155" s="0" t="s">
-        <v>678</v>
-      </c>
-      <c r="L155" s="0" t="s">
-        <v>679</v>
-      </c>
-      <c r="M155" s="0" t="s">
-        <v>680</v>
-      </c>
-      <c r="N155" s="0"/>
-      <c r="O155" s="0" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="0" t="s">
-        <v>682</v>
-      </c>
-      <c r="B156" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D156" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E156" s="0" t="s">
-        <v>683</v>
-      </c>
-      <c r="F156" s="11" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="G156" s="0"/>
-      <c r="H156" s="0"/>
-      <c r="I156" s="0"/>
-      <c r="J156" s="0"/>
-      <c r="K156" s="0" t="s">
-        <v>684</v>
-      </c>
-      <c r="L156" s="0" t="s">
-        <v>685</v>
-      </c>
-      <c r="M156" s="0" t="s">
-        <v>686</v>
-      </c>
-      <c r="N156" s="0"/>
-      <c r="O156" s="0" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="0" t="s">
-        <v>688</v>
-      </c>
-      <c r="B157" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D157" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E157" s="0" t="s">
-        <v>689</v>
-      </c>
-      <c r="F157" s="11" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="G157" s="0"/>
-      <c r="H157" s="0"/>
-      <c r="I157" s="0"/>
-      <c r="J157" s="0"/>
-      <c r="K157" s="0" t="s">
-        <v>690</v>
-      </c>
-      <c r="L157" s="0" t="s">
-        <v>691</v>
-      </c>
-      <c r="M157" s="0" t="s">
-        <v>692</v>
-      </c>
-      <c r="N157" s="0"/>
-      <c r="O157" s="0"/>
-    </row>
-    <row r="158" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="0" t="s">
-        <v>693</v>
-      </c>
-      <c r="B158" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D158" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E158" s="0" t="s">
-        <v>689</v>
-      </c>
-      <c r="F158" s="11" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="G158" s="0"/>
-      <c r="H158" s="0"/>
-      <c r="I158" s="0"/>
-      <c r="J158" s="0"/>
-      <c r="K158" s="0" t="s">
-        <v>694</v>
-      </c>
-      <c r="L158" s="0" t="s">
-        <v>695</v>
-      </c>
-      <c r="M158" s="0" t="s">
-        <v>696</v>
-      </c>
-      <c r="N158" s="0"/>
-      <c r="O158" s="0"/>
-    </row>
-    <row r="159" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="0" t="s">
-        <v>688</v>
-      </c>
-      <c r="B159" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D159" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E159" s="0" t="s">
-        <v>697</v>
-      </c>
-      <c r="F159" s="11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="G159" s="0"/>
-      <c r="H159" s="0"/>
-      <c r="I159" s="0"/>
-      <c r="J159" s="0"/>
-      <c r="K159" s="0" t="s">
-        <v>690</v>
-      </c>
-      <c r="L159" s="0" t="s">
-        <v>691</v>
-      </c>
-      <c r="M159" s="0" t="s">
-        <v>692</v>
-      </c>
-      <c r="N159" s="0"/>
-      <c r="O159" s="0"/>
-    </row>
-    <row r="160" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="0" t="s">
-        <v>693</v>
-      </c>
-      <c r="B160" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D160" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E160" s="0" t="s">
-        <v>697</v>
-      </c>
-      <c r="F160" s="11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="G160" s="0"/>
-      <c r="H160" s="0"/>
-      <c r="I160" s="0"/>
-      <c r="J160" s="0"/>
-      <c r="K160" s="0" t="s">
-        <v>694</v>
-      </c>
-      <c r="L160" s="0" t="s">
-        <v>695</v>
-      </c>
-      <c r="M160" s="0" t="s">
-        <v>696</v>
-      </c>
-      <c r="N160" s="0"/>
-      <c r="O160" s="0"/>
-    </row>
-    <row r="161" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="0" t="s">
-        <v>698</v>
-      </c>
-      <c r="B161" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D161" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E161" s="0" t="s">
-        <v>699</v>
-      </c>
-      <c r="F161" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G161" s="0"/>
-      <c r="H161" s="0"/>
-      <c r="I161" s="0"/>
-      <c r="J161" s="0"/>
-      <c r="K161" s="0" t="s">
-        <v>700</v>
-      </c>
-      <c r="L161" s="0" t="s">
-        <v>701</v>
-      </c>
-      <c r="M161" s="0" t="s">
-        <v>702</v>
-      </c>
-      <c r="N161" s="0"/>
-      <c r="O161" s="0"/>
-    </row>
-    <row r="162" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="0" t="s">
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="B162" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D162" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E162" s="0" t="s">
-        <v>704</v>
-      </c>
-      <c r="F162" s="11" t="n">
+      <c r="F164" s="10" t="n">
         <v>2.78</v>
       </c>
-      <c r="G162" s="0"/>
-      <c r="H162" s="0"/>
-      <c r="I162" s="0"/>
-      <c r="J162" s="0"/>
-      <c r="K162" s="0" t="s">
-        <v>705</v>
-      </c>
-      <c r="L162" s="0" t="s">
-        <v>706</v>
-      </c>
-      <c r="M162" s="0" t="s">
-        <v>707</v>
-      </c>
-      <c r="N162" s="0"/>
-      <c r="O162" s="0" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="0" t="s">
-        <v>709</v>
-      </c>
-      <c r="B163" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D163" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E163" s="0" t="s">
-        <v>704</v>
-      </c>
-      <c r="F163" s="11" t="n">
+      <c r="K164" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="L164" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="M164" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="N164" s="1"/>
+      <c r="O164" s="1" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="F165" s="10" t="n">
         <v>2.78</v>
       </c>
-      <c r="G163" s="0"/>
-      <c r="H163" s="0"/>
-      <c r="I163" s="0"/>
-      <c r="J163" s="0"/>
-      <c r="K163" s="0" t="s">
-        <v>710</v>
-      </c>
-      <c r="L163" s="0" t="s">
-        <v>711</v>
-      </c>
-      <c r="M163" s="0" t="s">
-        <v>712</v>
-      </c>
-      <c r="N163" s="0"/>
-      <c r="O163" s="0" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="164" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="0" t="s">
-        <v>714</v>
-      </c>
-      <c r="B164" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D164" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E164" s="0" t="s">
-        <v>704</v>
-      </c>
-      <c r="F164" s="11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="G164" s="0"/>
-      <c r="H164" s="0"/>
-      <c r="I164" s="0"/>
-      <c r="J164" s="0"/>
-      <c r="K164" s="0" t="s">
-        <v>668</v>
-      </c>
-      <c r="L164" s="0" t="s">
-        <v>669</v>
-      </c>
-      <c r="M164" s="0" t="s">
-        <v>670</v>
-      </c>
-      <c r="N164" s="0"/>
-      <c r="O164" s="0" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="165" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="0" t="s">
-        <v>715</v>
-      </c>
-      <c r="B165" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D165" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E165" s="0" t="s">
-        <v>704</v>
-      </c>
-      <c r="F165" s="11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="G165" s="0"/>
-      <c r="H165" s="0"/>
-      <c r="I165" s="0"/>
-      <c r="J165" s="0"/>
-      <c r="K165" s="0" t="s">
-        <v>716</v>
-      </c>
-      <c r="L165" s="0" t="s">
-        <v>717</v>
-      </c>
-      <c r="M165" s="0" t="s">
-        <v>718</v>
-      </c>
-      <c r="N165" s="0"/>
-      <c r="O165" s="0" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="166" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="0" t="s">
+      <c r="K165" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="B166" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D166" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="E166" s="0" t="s">
-        <v>704</v>
-      </c>
-      <c r="F166" s="11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="G166" s="0"/>
-      <c r="H166" s="0"/>
-      <c r="I166" s="0"/>
-      <c r="J166" s="0"/>
-      <c r="K166" s="0" t="s">
+      <c r="L165" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="L166" s="0" t="s">
+      <c r="M165" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="M166" s="0" t="s">
+      <c r="N165" s="1"/>
+      <c r="O165" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="N166" s="0"/>
-      <c r="O166" s="0" t="s">
-        <v>724</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O166">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Dernier"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="DERNIER/Baby"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -7691,7 +7558,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7704,586 +7570,586 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="L2" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="F3" s="1" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="E2" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="F2" s="0" t="n">
+      <c r="E5" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>3.89</v>
       </c>
-      <c r="K2" s="0" t="s">
-        <v>643</v>
-      </c>
-      <c r="L2" s="0" t="s">
-        <v>644</v>
-      </c>
-      <c r="M2" s="0" t="s">
-        <v>645</v>
-      </c>
-      <c r="O2" s="0" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>647</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="K5" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="F3" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>3.89</v>
       </c>
-      <c r="K3" s="0" t="s">
-        <v>648</v>
-      </c>
-      <c r="L3" s="0" t="s">
-        <v>649</v>
-      </c>
-      <c r="M3" s="0" t="s">
-        <v>650</v>
-      </c>
-      <c r="O3" s="0" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>652</v>
-      </c>
-      <c r="B4" s="0" t="s">
+      <c r="K6" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="D4" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="F4" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>3.89</v>
       </c>
-      <c r="K4" s="0" t="s">
-        <v>653</v>
-      </c>
-      <c r="L4" s="0" t="s">
-        <v>654</v>
-      </c>
-      <c r="M4" s="0" t="s">
-        <v>655</v>
-      </c>
-      <c r="O4" s="0" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>657</v>
-      </c>
-      <c r="B5" s="0" t="s">
+      <c r="K7" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="F8" s="1" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="E5" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="K5" s="0" t="s">
-        <v>658</v>
-      </c>
-      <c r="L5" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="M5" s="0" t="s">
-        <v>660</v>
-      </c>
-      <c r="O5" s="0" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>662</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="F6" s="0" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="K6" s="0" t="s">
-        <v>663</v>
-      </c>
-      <c r="L6" s="0" t="s">
-        <v>664</v>
-      </c>
-      <c r="M6" s="0" t="s">
-        <v>665</v>
-      </c>
-      <c r="O6" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="E11" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="F7" s="0" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="K7" s="0" t="s">
+      <c r="L18" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="L7" s="0" t="s">
+      <c r="M18" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="M7" s="0" t="s">
+      <c r="O18" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="O7" s="0" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>672</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="F8" s="0" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="K8" s="0" t="s">
-        <v>673</v>
-      </c>
-      <c r="L8" s="0" t="s">
-        <v>674</v>
-      </c>
-      <c r="M8" s="0" t="s">
-        <v>675</v>
-      </c>
-      <c r="O8" s="0" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>677</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="F9" s="0" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="K9" s="0" t="s">
-        <v>678</v>
-      </c>
-      <c r="L9" s="0" t="s">
-        <v>679</v>
-      </c>
-      <c r="M9" s="0" t="s">
-        <v>680</v>
-      </c>
-      <c r="O9" s="0" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>682</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>683</v>
-      </c>
-      <c r="F10" s="0" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="K10" s="0" t="s">
-        <v>684</v>
-      </c>
-      <c r="L10" s="0" t="s">
-        <v>685</v>
-      </c>
-      <c r="M10" s="0" t="s">
-        <v>686</v>
-      </c>
-      <c r="O10" s="0" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>688</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>727</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>689</v>
-      </c>
-      <c r="F11" s="0" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="K11" s="0" t="s">
-        <v>690</v>
-      </c>
-      <c r="L11" s="0" t="s">
-        <v>691</v>
-      </c>
-      <c r="M11" s="0" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>693</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>727</v>
-      </c>
-      <c r="E12" s="0" t="s">
-        <v>689</v>
-      </c>
-      <c r="F12" s="0" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="K12" s="0" t="s">
-        <v>694</v>
-      </c>
-      <c r="L12" s="0" t="s">
-        <v>695</v>
-      </c>
-      <c r="M12" s="0" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>688</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>727</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>697</v>
-      </c>
-      <c r="F13" s="0" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="K13" s="0" t="s">
-        <v>690</v>
-      </c>
-      <c r="L13" s="0" t="s">
-        <v>691</v>
-      </c>
-      <c r="M13" s="0" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>693</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>727</v>
-      </c>
-      <c r="E14" s="0" t="s">
-        <v>697</v>
-      </c>
-      <c r="F14" s="0" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="K14" s="0" t="s">
-        <v>694</v>
-      </c>
-      <c r="L14" s="0" t="s">
-        <v>695</v>
-      </c>
-      <c r="M14" s="0" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>698</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="E15" s="0" t="s">
-        <v>699</v>
-      </c>
-      <c r="F15" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" s="0" t="s">
-        <v>700</v>
-      </c>
-      <c r="L15" s="0" t="s">
-        <v>701</v>
-      </c>
-      <c r="M15" s="0" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="B16" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="E16" s="0" t="s">
-        <v>704</v>
-      </c>
-      <c r="F16" s="0" t="n">
+      <c r="F19" s="1" t="n">
         <v>2.78</v>
       </c>
-      <c r="K16" s="0" t="s">
-        <v>705</v>
-      </c>
-      <c r="L16" s="0" t="s">
-        <v>706</v>
-      </c>
-      <c r="M16" s="0" t="s">
-        <v>707</v>
-      </c>
-      <c r="O16" s="0" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>709</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D17" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="E17" s="0" t="s">
-        <v>704</v>
-      </c>
-      <c r="F17" s="0" t="n">
+      <c r="K19" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="F20" s="1" t="n">
         <v>2.78</v>
       </c>
-      <c r="K17" s="0" t="s">
-        <v>710</v>
-      </c>
-      <c r="L17" s="0" t="s">
-        <v>711</v>
-      </c>
-      <c r="M17" s="0" t="s">
-        <v>712</v>
-      </c>
-      <c r="O17" s="0" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>714</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="E18" s="0" t="s">
-        <v>704</v>
-      </c>
-      <c r="F18" s="0" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K18" s="0" t="s">
-        <v>668</v>
-      </c>
-      <c r="L18" s="0" t="s">
-        <v>669</v>
-      </c>
-      <c r="M18" s="0" t="s">
-        <v>670</v>
-      </c>
-      <c r="O18" s="0" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>715</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="E19" s="0" t="s">
-        <v>704</v>
-      </c>
-      <c r="F19" s="0" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K19" s="0" t="s">
-        <v>716</v>
-      </c>
-      <c r="L19" s="0" t="s">
-        <v>717</v>
-      </c>
-      <c r="M19" s="0" t="s">
-        <v>718</v>
-      </c>
-      <c r="O19" s="0" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="K20" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="B20" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="E20" s="0" t="s">
-        <v>704</v>
-      </c>
-      <c r="F20" s="0" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K20" s="0" t="s">
+      <c r="L20" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="L20" s="0" t="s">
+      <c r="M20" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="M20" s="0" t="s">
+      <c r="O20" s="1" t="s">
         <v>723</v>
-      </c>
-      <c r="O20" s="0" t="s">
-        <v>724</v>
       </c>
     </row>
   </sheetData>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="752">
   <si>
     <t xml:space="preserve">Nombre del producto</t>
   </si>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">DERNIER/Skinsept</t>
   </si>
   <si>
-    <t xml:space="preserve">200Grs</t>
+    <t xml:space="preserve">200g</t>
   </si>
   <si>
     <t xml:space="preserve">Solución limpiadora facial con AHA (0,15%) y Tea Tree Oil. Para pieles grasas, mixtas, secas y normales.</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">Crema Hidrantante Facial</t>
   </si>
   <si>
-    <t xml:space="preserve">75 G</t>
+    <t xml:space="preserve">75 g</t>
   </si>
   <si>
     <t xml:space="preserve">IMG-0014</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">Despigmentante Facial (CREMA HIDRATANTE ANTIMANCHAS ÁCIDO KÓJICO )</t>
   </si>
   <si>
-    <t xml:space="preserve">50 G</t>
+    <t xml:space="preserve">50 g</t>
   </si>
   <si>
     <t xml:space="preserve">Crema para tratamiento de hiperpigmentaciones y manchas con Ácido Kójico (1%). Uso nocturno.</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">Contorno De Ojos (RESVERATROL -CAFEINA)</t>
   </si>
   <si>
-    <t xml:space="preserve">20 G</t>
+    <t xml:space="preserve">20 g</t>
   </si>
   <si>
     <t xml:space="preserve">Crema/gel de contorno de ojos con Resveratrol (1%), Cafeína y Colágeno. Reduce bolsas, ojeras y arrugas.</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">Serum Protector Solar</t>
   </si>
   <si>
-    <t xml:space="preserve">30 G</t>
+    <t xml:space="preserve">30 g</t>
   </si>
   <si>
     <t xml:space="preserve">Sérum facial con Complejo de Filtros UVA/UVB, Complejo de Péptidos (1%), Colágeno Hidrolizado, Coenzima Q10 y Ácido Hialurónico.</t>
@@ -470,6 +470,9 @@
     <t xml:space="preserve">Protector Solar Facial</t>
   </si>
   <si>
+    <t xml:space="preserve">120g</t>
+  </si>
+  <si>
     <t xml:space="preserve">Protector solar facial con mezcla de filtros UV físicos y químicos, D-Panthenol, emolientes y emulsificantes.</t>
   </si>
   <si>
@@ -485,9 +488,6 @@
     <t xml:space="preserve">Mezcla de Filtros UV Físicos y Químicos (Dióxido de Titanio); D-Panthenol; Emolientes; Emulsificantes</t>
   </si>
   <si>
-    <t xml:space="preserve">120Ml</t>
-  </si>
-  <si>
     <t xml:space="preserve">Protector Solar Facial Con Color  Tono Light (Claro)</t>
   </si>
   <si>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">Protector En Polvo Translucido (Brocha)</t>
   </si>
   <si>
-    <t xml:space="preserve">7 G</t>
+    <t xml:space="preserve">7 g</t>
   </si>
   <si>
     <t xml:space="preserve">Protector solar en polvo con brocha dispensadora en tonos Translúcido, Light, Medium y Dark. Efecto mate, resistente al agua.</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">IMG-0043</t>
   </si>
   <si>
-    <t xml:space="preserve">img-0043.jpg</t>
+    <t xml:space="preserve">img-0200.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Deslizar la brocha de forma generosa y uniforme con movimientos circulares sobre todo el rostro y las zonas expuestas (orejas, cuello, escote y dorso de las manos) para garantizar la correcta liberación de producto. Evite mojar la brocha, ya que el polvo podría humedecerse y perder su efectividad de aplicación.</t>
@@ -572,18 +572,30 @@
     <t xml:space="preserve">Protector En Polvo Light (Brocha)</t>
   </si>
   <si>
+    <t xml:space="preserve">img-0201.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Protector En Polvo Medium (Brocha)</t>
   </si>
   <si>
+    <t xml:space="preserve">img-0202.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Protector en polvo dark (Brocha)</t>
   </si>
   <si>
+    <t xml:space="preserve">img-0203.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Protector Solar Spray + FRAGANCIA COCO 200ML</t>
   </si>
   <si>
     <t xml:space="preserve">DERNIER/Sun Care</t>
   </si>
   <si>
+    <t xml:space="preserve">200ml</t>
+  </si>
+  <si>
     <t xml:space="preserve">Protector solar aerosol 360° con Aloe Vera, Alfa Bisabolol, Ácido Hialurónico, Alfa Tocoferol y D-Panthenol.</t>
   </si>
   <si>
@@ -599,7 +611,7 @@
     <t xml:space="preserve">Complejo de Filtros UVA/UVB; Aloe Vera Extract; Alfa Bisabolol; Hyaluronic Acid; Alpha Tocopherol; D-Panthenol</t>
   </si>
   <si>
-    <t xml:space="preserve">PROTECTOR SOLAR EN CREMA SPF50+ 200ML</t>
+    <t xml:space="preserve">Protector Solar en Crema  SPF50+ 200ML</t>
   </si>
   <si>
     <t xml:space="preserve">Protector solar en crema y spray con filtros UV físicos/químicos y Extracto de Aloe Vera. Fotoprotector e hidratante.</t>
@@ -620,7 +632,16 @@
     <t xml:space="preserve">Protector Solar (Corporal) 50 +</t>
   </si>
   <si>
-    <t xml:space="preserve">160 G</t>
+    <t xml:space="preserve">75g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Img-0205.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Solucion Limpiadora Para la piel</t>
@@ -677,7 +698,7 @@
     <t xml:space="preserve">Crema Antipañalitis</t>
   </si>
   <si>
-    <t xml:space="preserve">50Gr</t>
+    <t xml:space="preserve">50g</t>
   </si>
   <si>
     <t xml:space="preserve">Crema protectora para el área del pañal con Óxido de Zinc. Calma, alivia la irritación e hipoalergénica.</t>
@@ -686,18 +707,21 @@
     <t xml:space="preserve">IMG-0103</t>
   </si>
   <si>
+    <t xml:space="preserve">img-0206.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplicar en la zona del pañal, previamente limpia y seca, con movimientos circulares hasta que la crema sea absorbida por la piel. Úsese en cada cambio de pañal, extendiéndola en forma uniforme. Es fácil de aplicar, extender y remover.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Óxido de Zinc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250g</t>
+  </si>
+  <si>
     <t xml:space="preserve">img-0103.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Aplicar en la zona del pañal, previamente limpia y seca, con movimientos circulares hasta que la crema sea absorbida por la piel. Úsese en cada cambio de pañal, extendiéndola en forma uniforme. Es fácil de aplicar, extender y remover.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Óxido de Zinc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250Gr</t>
-  </si>
-  <si>
     <t xml:space="preserve">Colonia</t>
   </si>
   <si>
@@ -722,27 +746,27 @@
     <t xml:space="preserve">IMG-0106</t>
   </si>
   <si>
+    <t xml:space="preserve">img-0207.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spray: Agítese bien antes de usar, aplíquelo directamente sobre la piel o la ropa rociándolo desde unos 10 o 20 cm. Para aplicarlo en el rostro rocíelo en la palma de la mano y luego extiéndalo sobre la cara y cuello, evitando los ojos, nariz y boca. Loción: Aplíquelo directamente sobre la piel. Para aplicarlo en el rostro, extiéndalo sobre la cara y cuello, evitando los ojos, nariz y boca.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geraniol; Citronella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repelente En Spray</t>
+  </si>
+  <si>
     <t xml:space="preserve">img-0106.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Spray: Agítese bien antes de usar, aplíquelo directamente sobre la piel o la ropa rociándolo desde unos 10 o 20 cm. Para aplicarlo en el rostro rocíelo en la palma de la mano y luego extiéndalo sobre la cara y cuello, evitando los ojos, nariz y boca. Loción: Aplíquelo directamente sobre la piel. Para aplicarlo en el rostro, extiéndalo sobre la cara y cuello, evitando los ojos, nariz y boca.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geraniol; Citronella</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repelente En Spray</t>
-  </si>
-  <si>
     <t xml:space="preserve">Protector En Crema Baby Colapsible</t>
   </si>
   <si>
     <t xml:space="preserve">DERNIER/Sun Care Baby</t>
   </si>
   <si>
-    <t xml:space="preserve">50Grs</t>
-  </si>
-  <si>
     <t xml:space="preserve">Protector solar para bebés con filtros minerales naturales (dióxido de titanio y óxido de zinc) y Extracto de Aloe Vera.</t>
   </si>
   <si>
@@ -758,7 +782,7 @@
     <t xml:space="preserve">Filtros Minerales Naturales (Dióxido de Titanio y Óxido de Zinc); Aloe Vera Extract</t>
   </si>
   <si>
-    <t xml:space="preserve">160Grs</t>
+    <t xml:space="preserve">img-0208.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Enjuague Bucal Kids</t>
@@ -767,129 +791,158 @@
     <t xml:space="preserve">DERNIER/Oral Care</t>
   </si>
   <si>
+    <t xml:space="preserve">250ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enjuague bucal infantil sin alcohol con sabor a cereza. Protección contra las caries.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0107.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vierte 10 mililitros (aproximadamente 2 cucharadas) de enjuague bucal en un vaso. Enjuaga la boca con el líquido durante 30 segundos, asegurándote de que pase por todas las áreas de la boca. Escupa el enjuague bucal en el lavabo. No tragar. Usar una vez al día, preferiblemente después del cepillado nocturno.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solucion Limpiadora Para La Higiene Intima (NEUTRO ALOE VERA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jabón íntimo con Chamomilla Recutita, Aloe Barbadensis y Glicerina. Control de olor y pH adecuado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0056.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Humedecer sus partes íntimas con agua fresca, colocar una porción del producto sobre la palma de la mano y extender sobre la zona con suaves movimientos circulares. Enjuague con abundante agua. Repita de ser necesario.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamomilla Recutita Flower Extract; Aloe Barbadensis Extract; Glicerina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solucion Limpiadora Para  Manos Y Cuerpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solución de uso diario para limpiar la piel, por su acción bactericida y su contenido de ácidos frutales (AHA) tiene un excelente potencial germicida que ayudará a eliminar las impurezas de la piel, proporcionando una sensación de máxima frescura e higiene. Inhibe el crecimiento de bacterias, hongos y levaduras. Dejará tu piel limpia, suave y luminosa sin irritarla.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0209.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water, Sodium Laureth Sulphate, Cocamide DEA, Glycerin, Sodium Chloride, Glycol Distearate, Cocamidopropyl   Betaine,   Citric   Acid,   Diazolidinyl   Urea, Tea Tree Oil, Fragrance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repelente de Insectos Locion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repelente de insectos natural con Geraniol y Citronella. Protección duradera no grasosa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0055.jpg</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="22"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Repelente de Insectos Spray
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0210.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menthol Gel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DERNIER/Dolout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gel muscular analgésico y antiinflamatorio con Alcanfor, Mentol, Salicilato de Metilo y Aloe Vera.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0057.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antes del Ejercicio: Aplica una cantidad moderada de Menthol Gel Dol Out en las áreas musculares que vas a trabajar. Masajea suavemente hasta que el producto se absorba completamente. Después del Ejercicio: Vuelve a aplicar el mentol en las áreas trabajadas para ayudar a reducir la inflamación y aliviar el dolor muscular. Masajea hasta su completa absorción.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camphor (Alcanfor); Menthol (Mentol); Methyl Salicylate (Salicilato de Metilo); Aloe Barbadensis Leaf Extract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arnica Montana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gel analgésico y calmante con Alcanfor, Mentol, Extracto de Árnica Montana, Aloe Vera y Fucus Vesiculosus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0058.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplica una capa delgada de gel de árnica montana en el área afectada. Masajea suavemente hasta que el gel se absorba completamente. Repite la aplicación 3 veces al día o según sea necesario. Evita el contacto con los ojos, mucosas y heridas abiertas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camphor; Menthol; Árnica Montana Flower Extract; Aloe Barbadensis Extract; Fucus Vesiculosus Extract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anti-Transpirante El</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90Ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antitranspirante masculino con Clorhidróxido de Aluminio, Caléndula, Manzanilla y Alumbre de Amonio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0060.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asegúrate de que la piel esté limpia y seca antes de aplicar el antitranspirante. Aplica una capa uniforme en las axilas. Deja que el producto se seque completamente antes de vestirte. Utiliza el antitranspirante una vez al día, preferiblemente después de la ducha.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aluminium Chlorhydroxide; Caléndula Officinalis Extract; Chamomilla Recutita Extract; Ammonium Alum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anti-Transpirante Ella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antitranspirante con Clorhidróxido de Aluminio, Extracto de Caléndula, Manzanilla y Alumbre de Amonio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0059.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enjuague Bucal</t>
+  </si>
+  <si>
     <t xml:space="preserve">250Ml</t>
   </si>
   <si>
-    <t xml:space="preserve">Enjuague bucal infantil sin alcohol con sabor a cereza. Protección contra las caries.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0107.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vierte 10 mililitros (aproximadamente 2 cucharadas) de enjuague bucal en un vaso. Enjuaga la boca con el líquido durante 30 segundos, asegurándote de que pase por todas las áreas de la boca. Escupa el enjuague bucal en el lavabo. No tragar. Usar una vez al día, preferiblemente después del cepillado nocturno.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solucion Limpiadora Para La Higiene Intima (NEUTRO ALOE VERA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jabón íntimo con Chamomilla Recutita, Aloe Barbadensis y Glicerina. Control de olor y pH adecuado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0056.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Humedecer sus partes íntimas con agua fresca, colocar una porción del producto sobre la palma de la mano y extender sobre la zona con suaves movimientos circulares. Enjuague con abundante agua. Repita de ser necesario.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chamomilla Recutita Flower Extract; Aloe Barbadensis Extract; Glicerina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solucion Limpiadora Para  Manos Y Cuerpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repelente de insectos natural con Geraniol y Citronella. Protección duradera no grasosa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0055.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menthol Gel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DERNIER/Dolout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250Grs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gel muscular analgésico y antiinflamatorio con Alcanfor, Mentol, Salicilato de Metilo y Aloe Vera.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0057.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antes del Ejercicio: Aplica una cantidad moderada de Menthol Gel Dol Out en las áreas musculares que vas a trabajar. Masajea suavemente hasta que el producto se absorba completamente. Después del Ejercicio: Vuelve a aplicar el mentol en las áreas trabajadas para ayudar a reducir la inflamación y aliviar el dolor muscular. Masajea hasta su completa absorción.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camphor (Alcanfor); Menthol (Mentol); Methyl Salicylate (Salicilato de Metilo); Aloe Barbadensis Leaf Extract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arnica Montana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gel analgésico y calmante con Alcanfor, Mentol, Extracto de Árnica Montana, Aloe Vera y Fucus Vesiculosus.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0058.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplica una capa delgada de gel de árnica montana en el área afectada. Masajea suavemente hasta que el gel se absorba completamente. Repite la aplicación 3 veces al día o según sea necesario. Evita el contacto con los ojos, mucosas y heridas abiertas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camphor; Menthol; Árnica Montana Flower Extract; Aloe Barbadensis Extract; Fucus Vesiculosus Extract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anti-Transpirante El</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90Ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antitranspirante masculino con Clorhidróxido de Aluminio, Caléndula, Manzanilla y Alumbre de Amonio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0060.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asegúrate de que la piel esté limpia y seca antes de aplicar el antitranspirante. Aplica una capa uniforme en las axilas. Deja que el producto se seque completamente antes de vestirte. Utiliza el antitranspirante una vez al día, preferiblemente después de la ducha.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aluminium Chlorhydroxide; Caléndula Officinalis Extract; Chamomilla Recutita Extract; Ammonium Alum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anti-Transpirante Ella</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antitranspirante con Clorhidróxido de Aluminio, Extracto de Caléndula, Manzanilla y Alumbre de Amonio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0059.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enjuague Bucal</t>
-  </si>
-  <si>
     <t xml:space="preserve">Enjuague bucal contra caries y placa bacteriana sin alcohol sabor a menta fresca.</t>
   </si>
   <si>
@@ -905,7 +958,7 @@
     <t xml:space="preserve">Parches de Gel Revitalizantes para el Contorno de Ojos (OJOS CAFEINA)</t>
   </si>
   <si>
-    <t xml:space="preserve">100Grs</t>
+    <t xml:space="preserve">100g</t>
   </si>
   <si>
     <t xml:space="preserve">Pads de gel descongestivos con Cafeína (0,5%), Camellia Sinensis (3%) y Ácido Hialurónico (0,75%). 80 pads.</t>
@@ -1001,19 +1054,31 @@
     <t xml:space="preserve">Protector Solar Baby Crema SPF50+ 200CC</t>
   </si>
   <si>
-    <t xml:space="preserve">Cc stick luminous (LIGHT) (PROTECTOR SOLAR EFECTO FILTRO)</t>
+    <t xml:space="preserve">img-0211.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC stick luminous (LIGHT) (PROTECTOR SOLAR EFECTO FILTRO)</t>
   </si>
   <si>
     <t xml:space="preserve">DERNIER</t>
   </si>
   <si>
-    <t xml:space="preserve">30GRS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cc stick luminous (MEDIUM) (PROTECTOR SOLAR EFECTO FILTRO)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cc stick luminous (DARK) (PROTECTOR SOLAR EFECTO FILTRO)</t>
+    <t xml:space="preserve">30g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cc_stick_light_2.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC stick luminous (MEDIUM) (PROTECTOR SOLAR EFECTO FILTRO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cc_stick_medio_2.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC stick luminous (DARK) (PROTECTOR SOLAR EFECTO FILTRO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cc_stick_dark_2.webp</t>
   </si>
   <si>
     <t xml:space="preserve">SMART BODY SERUM ANTIEDAD RETINAL  200ML</t>
@@ -1076,9 +1141,6 @@
     <t xml:space="preserve">GEL ANTIBACTERIAL</t>
   </si>
   <si>
-    <t xml:space="preserve">200ML</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gel antibacterial con 62% Alcohol, Cloruro de Benzalconio, Vitamina E y Aloe Vera. Elimina 99,9% de gérmenes.</t>
   </si>
   <si>
@@ -1097,25 +1159,42 @@
     <t xml:space="preserve">SERUM DE MICROAGUJAS NIVEL 1 30ML</t>
   </si>
   <si>
-    <t xml:space="preserve">30ML</t>
+    <t xml:space="preserve">30ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diseñado para quienes inician sus rutinas de dermoestimulación, este sérum ofrece una experiencia cómoda y segura gracias a su bbaja concentración de microagujas. Ideal para pieles sensibles o usuarios nuevos que buscan revitalizar su piel sin irritaciones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imagen_base_Serumdemicroagujas-3.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toma una cantidad apropiada del producto y extiéndelo suavemente de manera uniforme sobre la piel completamente limpia y seca hasta su completa absorción, evitando el área de los ojos. Usar 3 a 4 veces por semana, preferiblemente durante la noche o diariamente si ya tu piel se ha adaptado.
+Este paso prepara la piel para mejorar la absorción de productos aplicados.</t>
   </si>
   <si>
     <t xml:space="preserve">SERUM DE MICROAGUJAS NIVEL 2 30ML</t>
   </si>
   <si>
+    <t xml:space="preserve">Sérum con microagujas de intensidad media, diseñado para usuarios que ya han experimentado rutinas suaves y desean avanzar hacia una estimulación más efectiva sin perder confort. Ideal como paso intermedio para obtener resultados visibles con mayor firmeza y regeneración.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imagen_base_Serumdemicroagujas-2.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toma una cantidad apropiada del producto y extiéndelo suavemente de manera uniforme sobre la piel completamente limpia y seca hasta su completa absorción, evitando el área de los ojos. Usar 2 a 3 veces por semana, preferiblemente durante la noche. Este paso potencia la absorción de productos aplicados posteriormente (como hidratantes, antioxidantes o tratamientos nutritivos) y ayuda a mejorar la textura y suavidad de la piel.</t>
+  </si>
+  <si>
     <t xml:space="preserve">SERUM DE MICROAGUJAS NIVEL 3 30ML</t>
   </si>
   <si>
-    <t xml:space="preserve">DERNIER CAPSULE CREAM REPARADORA PDRN Y EXOSOMAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DERNIER CAPSULE CREAM MANCHAS ÁCIDO TRANEXAMICO Y VIT C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DERNIER CAPSULE CREAM MATIFICANTE ZINC PCA Y PEPTIDOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DERNIER CAPSULE CREAM REAFIRMANTE NAD+ Y COLAGENO PEPTIDOS</t>
+    <t xml:space="preserve">Formulado para usuarios avanzados o profesionales, este serum de alta intensidad ofrece una acción profunda con tecnología de microagujas de última generación.
+Indicado para pieles resistentes y tratamientos de transformación visible, mejora significativamente firmeza, elasticidad y textura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imagen_base_Serumdemicroagujas-1.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toma una cantidad apropiada del producto y extiéndelo suavemente de manera uniforme sobre la piel completamente limpia y seca hasta su completa absorción, evitando el área de los ojos. Usar 1 vez por semana, preferiblemente durante la noche. Este paso renueva tu piel y potencia la absorción de productos aplicados posteriormente (como hidratantes, antioxidantes o tratamientos nutritivos), mejora la firmeza, textura y suavidad de la piel.</t>
   </si>
   <si>
     <t xml:space="preserve">GEL LIMPIADOR FACIAL ANTIEDAD SALMON</t>
@@ -1124,13 +1203,40 @@
     <t xml:space="preserve">DERNIER/PDRN</t>
   </si>
   <si>
+    <t xml:space="preserve">Tratamiento de higiene facial de alta precisión diseñado para disolver impurezas con delicadeza mientras redensifica y aporta firmeza a la piel. Su fórmula fluida genera una espuma ligera que libera una potente red de activos moleculares. Ideal para elevar la rutina diaria y despertar la juventud del rostro desde el primer paso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">web-pdrn-3.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosificar una pequeña cantidad de la solución jabonosa sobre las palmas de las manos húmedas y frotar hasta generar una delicada espuma. Aplicar sobre el rostro húmedo mediante suaves masajes circulares. Enjuagar con abundante agua. Secar a toques suaves con una toalla limpia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ginseng Leaf Water, Exosomas (5000 ppm), PDRN &amp; Pantenol, Ácido Hialurónico Hidrolizado, Vitamina E: protecc</t>
+  </si>
+  <si>
     <t xml:space="preserve">SERUM FACIAL ANTIEDAD PDRN SALMON</t>
   </si>
   <si>
+    <t xml:space="preserve">web-pdrn-2.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con el rostro limpio y seco, aplicar de 3 a 5 gotas sobre la cara, cuello y escote. Realizar suaves masajes ascendentes hasta su completa absorción. Utilizar mañana y noche antes de su crema habitual. En el día, complementar con protector solar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDRN (Sodium DNA 30 000 ppm), Exosomas de Centella Asiática (50 000 ppm), Niacinamida, Péptidos de Colágeno Hidrolizado, Ácido Hialurónico Hidrolizado, Pantenol &amp; Beta-Glucano</t>
+  </si>
+  <si>
     <t xml:space="preserve">AQUA GEL HIDRANTANTE FACIAL ANTIEDAD (CREMA FACIAL-SALMON)</t>
   </si>
   <si>
-    <t xml:space="preserve">50GR</t>
+    <t xml:space="preserve">web-pdrn-1.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosificar una cantidad suficiente del gel sobre las yemas de los dedos y extender uniformemente con movimientos ascendentes sobre la piel limpia y seca del rostro, cuello y escote. Masajear suavemente hasta su total absorción. Utilizar diariamente en la mañana y en la noche. Para optimizar el cuidado de la piel y prevenir los signos visibles del fotoenvejecimiento, se recomienda aplicar protector solar durante el día.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDRN Vegetal, Exosomas de Centella Asiática, Ácido Poliglutámico &amp; 8 Pesos Moleculares de Ácido Hialurónico, Ectoína, Vitamina E</t>
   </si>
   <si>
     <t xml:space="preserve">BRUCEN ADULTCARE BODY LOTION   400 ML</t>
@@ -1142,7 +1248,7 @@
     <t xml:space="preserve">LINEA BRUCEN ADULTCARE</t>
   </si>
   <si>
-    <t xml:space="preserve">400ML</t>
+    <t xml:space="preserve">400ml</t>
   </si>
   <si>
     <t xml:space="preserve">250ML</t>
@@ -1166,7 +1272,7 @@
     <t xml:space="preserve">BRUCEN ADULTCARE CREMA DERMOPROTECTORA ADULTO 100GR</t>
   </si>
   <si>
-    <t xml:space="preserve">100ML</t>
+    <t xml:space="preserve">100ml</t>
   </si>
   <si>
     <t xml:space="preserve">Crema dermoprotectora para prevención de escaras y zona expuesta al pañal. Con Óxido de Zinc, Vitamina E, Alantoína, Glicerina y Aloe Vera.</t>
@@ -1184,9 +1290,6 @@
     <t xml:space="preserve">BRUCEN ADULTACARE CREMA DERMORESTAURADORA  CON CENTELLA ASIATICA 30 GR</t>
   </si>
   <si>
-    <t xml:space="preserve">30GR</t>
-  </si>
-  <si>
     <t xml:space="preserve">Crema cicatrizante para herida y ulceraciones cutáneas con Centella Asiática, Vitamina E, Alantoína, Glicerina y Aloe Vera.</t>
   </si>
   <si>
@@ -1220,9 +1323,6 @@
     <t xml:space="preserve">BRUCEN PANTALLA SOLAR PARA  EL CUERPO 100 GR</t>
   </si>
   <si>
-    <t xml:space="preserve">100GR</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pantalla solar corporal fragancia Coco Mandarina con filtros químicos/minerales, Vitamina E y D-Panthenol.</t>
   </si>
   <si>
@@ -1235,7 +1335,7 @@
     <t xml:space="preserve">BRUCEN CREMA NUTRITIVA Y RESTAURADORA  CON  D-PANTENOL Y COLAGENO  80 GR</t>
   </si>
   <si>
-    <t xml:space="preserve">80GR</t>
+    <t xml:space="preserve">80g</t>
   </si>
   <si>
     <t xml:space="preserve">Crema facial nutritiva con Coenzima Q10, Colágeno, Glicerina, Aloe Vera, Triticum Vulgare, D-Panthenol y Vitamina E.</t>
@@ -1289,7 +1389,7 @@
     <t xml:space="preserve">LINEA ANTIACNE</t>
   </si>
   <si>
-    <t xml:space="preserve">120ML</t>
+    <t xml:space="preserve">120ml</t>
   </si>
   <si>
     <t xml:space="preserve">Dermolimpiador facial syndet para pieles con acné. Con Niacinamida y Ácido Salicílico.</t>
@@ -1322,7 +1422,7 @@
     <t xml:space="preserve">BRUCEN GEL CREMA ANTIACNE 20 GR</t>
   </si>
   <si>
-    <t xml:space="preserve">20GR</t>
+    <t xml:space="preserve">20g</t>
   </si>
   <si>
     <t xml:space="preserve">Gel crema comedolítico con Niacinamida, Ácido Salicílico, Centella Asiática, D-Panthenol y Óxido de Zinc.</t>
@@ -1361,9 +1461,6 @@
     <t xml:space="preserve">BRUCEN HYDRO GEL HIDRATANTE PARA PIELES GRASAS</t>
   </si>
   <si>
-    <t xml:space="preserve">120ml</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gel hidratante matificante con Niacinamida y D-Panthenol. Reduce la producción de sebo y atenúa manchas.</t>
   </si>
   <si>
@@ -1391,9 +1488,6 @@
     <t xml:space="preserve">BRUCEN NUTRITIVA CON ACIDO HIALURONICO 1%</t>
   </si>
   <si>
-    <t xml:space="preserve">80Grs</t>
-  </si>
-  <si>
     <t xml:space="preserve">Crema nutritiva con Ácido Hialurónico (1%) y D-Panthenol. Hidratación profunda multinivel y reducción de arrugas.</t>
   </si>
   <si>
@@ -1409,7 +1503,7 @@
     <t xml:space="preserve">BRUCEN HYDRO CLEAN BARRA DERMOLIMPIADORA PIEL SECA</t>
   </si>
   <si>
-    <t xml:space="preserve">90Grs</t>
+    <t xml:space="preserve">90g</t>
   </si>
   <si>
     <t xml:space="preserve">Barra dermolimpiadora para piel seca con Urea, D-Panthenol y Niacinamida. Hidratación multinivel.</t>
@@ -1625,7 +1719,7 @@
     <t xml:space="preserve">CREMA CORPORAL EXTRA HIDRATANTE BRU DIA B SKIN 220 ML</t>
   </si>
   <si>
-    <t xml:space="preserve">220ML</t>
+    <t xml:space="preserve">220ml</t>
   </si>
   <si>
     <t xml:space="preserve">GEL LIMPIADOR SYNDET BRU DIA B SKIN PARA ROSTRO Y CUERPO 250 ML</t>
@@ -1640,9 +1734,6 @@
     <t xml:space="preserve">LINEA  CICABRU</t>
   </si>
   <si>
-    <t xml:space="preserve">30 GR</t>
-  </si>
-  <si>
     <t xml:space="preserve">CICABRU AQUASEPT SOLUCION ANTISEPTICA ACIDO HIPOCLOROSO 120 ML</t>
   </si>
   <si>
@@ -1667,7 +1758,7 @@
     <t xml:space="preserve">Mentol; Alcanfor</t>
   </si>
   <si>
-    <t xml:space="preserve">35G</t>
+    <t xml:space="preserve">35g</t>
   </si>
   <si>
     <t xml:space="preserve">Borocanfor original</t>
@@ -1733,7 +1824,7 @@
     <t xml:space="preserve">Selenil Hidratacion Tratamiento Capilar</t>
   </si>
   <si>
-    <t xml:space="preserve">108ML</t>
+    <t xml:space="preserve">108ml</t>
   </si>
   <si>
     <t xml:space="preserve">Champú con Disulfuro de Selenio y Aceite de Almendras para cuero cabelludo normal a seco con caspa suelta.</t>
@@ -1769,9 +1860,6 @@
     <t xml:space="preserve">DG GODAN</t>
   </si>
   <si>
-    <t xml:space="preserve">400ml</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tratamiento capilar enriquecedor, shampoo sin sodio limpieza total y acondicionador vegano.</t>
   </si>
   <si>
@@ -2069,9 +2157,6 @@
     <t xml:space="preserve">GEL INTIMO NATURE PH 5.5</t>
   </si>
   <si>
-    <t xml:space="preserve">220ml</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jabón de ducha íntima femenina con Ácido Láctico, hipoalergénico y aprobado dermatológicamente.</t>
   </si>
   <si>
@@ -2087,121 +2172,124 @@
     <t xml:space="preserve">GEL FIJADOR ANTICAIDA</t>
   </si>
   <si>
+    <t xml:space="preserve">500g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gel fijador masculino fórmula anti-caída, sin residuos, sin alcohol, fijación duradera.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0125.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEL FIJADOR CRECE PELO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gel fijador masculino estimulador del crecimiento, sin residuos, sin alcohol, aporta brillo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0124.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTITRASPIRANTE SACHET 30 UND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desodorante antitranspirante 48h de protección contra el sudor y mal olor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0094.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACEITE CORPORAL ALMENDRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aceite corporal suavizante y nutritivo con Aceite de Almendras.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0093.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aceite de Almendras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACEITE CORPORAL COCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aceite corporal nutritivo para todo tipo de piel con fragancia/extracto de Coco.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0089.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACEITE CORPORAL ARGAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACEITE CORPORAL ROSA MOSQUETA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aceite corporal regenerador con Rosa Mosqueta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0090.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosa Mosqueta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACEITE CORPORAL Q10+COLAGENO ARGAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aceite corporal reafirmante con Coenzima Q10 y Colágeno.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG-0092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img-0092.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coenzima Q10; Colágeno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuidado Corporal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuidado Infantil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuidado Capilar</t>
+  </si>
+  <si>
     <t xml:space="preserve">500grs</t>
   </si>
   <si>
-    <t xml:space="preserve">Gel fijador masculino fórmula anti-caída, sin residuos, sin alcohol, fijación duradera.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0125.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GEL FIJADOR CRECE PELO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gel fijador masculino estimulador del crecimiento, sin residuos, sin alcohol, aporta brillo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0124.jpg</t>
-  </si>
-  <si>
     <t xml:space="preserve">120grs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANTITRASPIRANTE SACHET 30 UND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desodorante antitranspirante 48h de protección contra el sudor y mal olor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0094.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACEITE CORPORAL ALMENDRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aceite corporal suavizante y nutritivo con Aceite de Almendras.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0093.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aceite de Almendras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACEITE CORPORAL COCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aceite corporal nutritivo para todo tipo de piel con fragancia/extracto de Coco.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0089.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACEITE CORPORAL ARGAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACEITE CORPORAL ROSA MOSQUETA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aceite corporal regenerador con Rosa Mosqueta.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0090.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosa Mosqueta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACEITE CORPORAL Q10+COLAGENO ARGAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aceite corporal reafirmante con Coenzima Q10 y Colágeno.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG-0092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img-0092.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coenzima Q10; Colágeno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuidado Corporal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuidado Infantil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuidado Capilar</t>
   </si>
 </sst>
 </file>
@@ -2214,7 +2302,7 @@
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2242,8 +2330,31 @@
       <family val="1"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="22"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0E1B4D"/>
+      <name val="Montserrat;sans-serif"/>
+      <family val="0"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2252,14 +2363,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF6D"/>
-        <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFD8CE"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -2297,7 +2402,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2334,11 +2439,43 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2351,31 +2488,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFD8CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF6D"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -2413,11 +2525,11 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF6D"/>
+      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFD8CE"/>
+      <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -2426,7 +2538,7 @@
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF0E1B4D"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
@@ -2447,37 +2559,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18A303"/>
+        <a:srgbClr val="18a303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369A3"/>
+        <a:srgbClr val="0369a3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A33E03"/>
+        <a:srgbClr val="a33e03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8E03A3"/>
+        <a:srgbClr val="8e03a3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="C99C00"/>
+        <a:srgbClr val="c99c00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="C9211E"/>
+        <a:srgbClr val="c9211e"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000EE"/>
+        <a:srgbClr val="0000ee"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551A8B"/>
+        <a:srgbClr val="551a8b"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -2550,8 +2662,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W165"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:W233"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="68.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.33"/>
@@ -2599,7 +2711,7 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
@@ -2615,7 +2727,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="102.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
         <v>15</v>
       </c>
@@ -2636,7 +2748,7 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="L2" s="3" t="s">
@@ -2673,7 +2785,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L3" s="3" t="s">
@@ -2710,7 +2822,7 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="L4" s="3" t="s">
@@ -2747,7 +2859,7 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="2" t="s">
         <v>38</v>
       </c>
       <c r="L5" s="3" t="s">
@@ -2763,7 +2875,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="69" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
         <v>43</v>
       </c>
@@ -2784,7 +2896,7 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="K6" s="2"/>
       <c r="L6" s="3" t="s">
         <v>45</v>
       </c>
@@ -2819,7 +2931,7 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="2" t="s">
         <v>50</v>
       </c>
       <c r="L7" s="3" t="s">
@@ -2856,7 +2968,7 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="2" t="s">
         <v>56</v>
       </c>
       <c r="L8" s="3" t="s">
@@ -2893,7 +3005,7 @@
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="2" t="s">
         <v>63</v>
       </c>
       <c r="L9" s="3" t="s">
@@ -2930,7 +3042,7 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="2" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="3" t="s">
@@ -2967,7 +3079,7 @@
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="2" t="s">
         <v>77</v>
       </c>
       <c r="L11" s="3" t="s">
@@ -3005,7 +3117,7 @@
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
-      <c r="K12" s="3" t="s">
+      <c r="K12" s="2" t="s">
         <v>83</v>
       </c>
       <c r="L12" s="3" t="s">
@@ -3021,7 +3133,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="80.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
         <v>88</v>
       </c>
@@ -3042,7 +3154,7 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="3" t="s">
+      <c r="K13" s="2" t="s">
         <v>89</v>
       </c>
       <c r="L13" s="3" t="s">
@@ -3058,7 +3170,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="69" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
         <v>94</v>
       </c>
@@ -3079,7 +3191,7 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="3" t="s">
+      <c r="K14" s="2" t="s">
         <v>95</v>
       </c>
       <c r="L14" s="3" t="s">
@@ -3117,7 +3229,7 @@
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="3" t="s">
+      <c r="K15" s="2" t="s">
         <v>101</v>
       </c>
       <c r="L15" s="3" t="s">
@@ -3134,7 +3246,7 @@
       </c>
       <c r="R15" s="8"/>
     </row>
-    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="46.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
         <v>106</v>
       </c>
@@ -3155,7 +3267,7 @@
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="3" t="s">
+      <c r="K16" s="2" t="s">
         <v>107</v>
       </c>
       <c r="L16" s="3" t="s">
@@ -3172,7 +3284,7 @@
       </c>
       <c r="R16" s="8"/>
     </row>
-    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="57.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
         <v>112</v>
       </c>
@@ -3193,7 +3305,7 @@
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
-      <c r="K17" s="3" t="s">
+      <c r="K17" s="2" t="s">
         <v>113</v>
       </c>
       <c r="L17" s="3" t="s">
@@ -3231,7 +3343,7 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
-      <c r="K18" s="3" t="s">
+      <c r="K18" s="2" t="s">
         <v>119</v>
       </c>
       <c r="L18" s="3" t="s">
@@ -3268,7 +3380,7 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
-      <c r="K19" s="3" t="s">
+      <c r="K19" s="2" t="s">
         <v>125</v>
       </c>
       <c r="L19" s="3" t="s">
@@ -3306,7 +3418,7 @@
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="3" t="s">
+      <c r="K20" s="2" t="s">
         <v>131</v>
       </c>
       <c r="L20" s="3" t="s">
@@ -3323,7 +3435,7 @@
       </c>
       <c r="Q20" s="8"/>
     </row>
-    <row r="21" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="80.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
         <v>136</v>
       </c>
@@ -3344,7 +3456,7 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
-      <c r="K21" s="3" t="s">
+      <c r="K21" s="2" t="s">
         <v>137</v>
       </c>
       <c r="L21" s="3" t="s">
@@ -3361,7 +3473,7 @@
       </c>
       <c r="T21" s="8"/>
     </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="35.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
         <v>142</v>
       </c>
@@ -3382,7 +3494,7 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
-      <c r="K22" s="3" t="s">
+      <c r="K22" s="2" t="s">
         <v>143</v>
       </c>
       <c r="L22" s="3" t="s">
@@ -3399,7 +3511,7 @@
       </c>
       <c r="V22" s="8"/>
     </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="46.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
         <v>148</v>
       </c>
@@ -3416,29 +3528,33 @@
       <c r="F23" s="7" t="n">
         <v>4.74666666666667</v>
       </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
+      <c r="G23" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>6.66666666666667</v>
+      </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="3" t="s">
-        <v>149</v>
+      <c r="K23" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="57.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>16</v>
@@ -3448,34 +3564,34 @@
         <v>17</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>154</v>
+        <v>62</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>6.66666666666667</v>
+        <v>7.57333333333333</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
-      <c r="K24" s="3" t="s">
-        <v>149</v>
+      <c r="K24" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="57.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>16</v>
@@ -3494,14 +3610,14 @@
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
-      <c r="K25" s="3" t="s">
-        <v>156</v>
+      <c r="K25" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="N25" s="5" t="s">
         <v>159</v>
@@ -3510,9 +3626,9 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="57.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>16</v>
@@ -3531,14 +3647,14 @@
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
-      <c r="K26" s="3" t="s">
-        <v>162</v>
+      <c r="K26" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N26" s="5" t="s">
         <v>159</v>
@@ -3547,9 +3663,9 @@
         <v>160</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="57.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>16</v>
@@ -3562,31 +3678,31 @@
         <v>62</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>7.57333333333333</v>
+        <v>7.25333333333333</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
-      <c r="K27" s="3" t="s">
-        <v>166</v>
+      <c r="K27" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>16</v>
@@ -3596,34 +3712,34 @@
         <v>17</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>62</v>
+        <v>176</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>7.25333333333333</v>
+        <v>7.70666666666667</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
-      <c r="K28" s="3" t="s">
-        <v>170</v>
+      <c r="K28" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="N28" s="5" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>16</v>
@@ -3642,14 +3758,14 @@
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
-      <c r="K29" s="3" t="s">
+      <c r="K29" s="2" t="s">
         <v>177</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>179</v>
+      <c r="M29" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="N29" s="5" t="s">
         <v>180</v>
@@ -3659,8 +3775,8 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9" t="s">
-        <v>182</v>
+      <c r="A30" s="6" t="s">
+        <v>184</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>16</v>
@@ -3679,14 +3795,14 @@
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
-      <c r="K30" s="3" t="s">
+      <c r="K30" s="2" t="s">
         <v>177</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="M30" s="3" t="s">
-        <v>179</v>
+      <c r="M30" s="9" t="s">
+        <v>185</v>
       </c>
       <c r="N30" s="5" t="s">
         <v>180</v>
@@ -3696,8 +3812,8 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9" t="s">
-        <v>183</v>
+      <c r="A31" s="6" t="s">
+        <v>186</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>16</v>
@@ -3716,14 +3832,14 @@
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
-      <c r="K31" s="3" t="s">
+      <c r="K31" s="2" t="s">
         <v>177</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="M31" s="3" t="s">
-        <v>179</v>
+      <c r="M31" s="9" t="s">
+        <v>187</v>
       </c>
       <c r="N31" s="5" t="s">
         <v>180</v>
@@ -3732,53 +3848,53 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9" t="s">
-        <v>184</v>
+    <row r="32" customFormat="false" ht="69" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>188</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3" t="s">
-        <v>17</v>
+        <v>189</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>7.70666666666667</v>
+        <v>7.89333333333333</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
-      <c r="K32" s="3" t="s">
-        <v>177</v>
+      <c r="K32" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="N32" s="5" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9" t="s">
-        <v>185</v>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="80.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>18</v>
@@ -3790,537 +3906,537 @@
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
-      <c r="K33" s="3" t="s">
-        <v>187</v>
+      <c r="K33" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="N33" s="5" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9" t="s">
-        <v>192</v>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="80.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>202</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>186</v>
+        <v>17</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>7.89333333333333</v>
-      </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
+        <v>5.76</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>8.38666666666667</v>
+      </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="3" t="s">
-        <v>193</v>
+      <c r="K34" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="N34" s="5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9" t="s">
-        <v>198</v>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>207</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3" t="s">
-        <v>17</v>
+        <v>208</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>5.76</v>
+        <v>2.88</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
-      <c r="K35" s="3" t="s">
-        <v>193</v>
+      <c r="K35" s="2" t="s">
+        <v>209</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="N35" s="5" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9" t="s">
-        <v>198</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3" t="s">
-        <v>17</v>
+        <v>208</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>8.38666666666667</v>
+        <v>2.90666666666667</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
-      <c r="K36" s="3" t="s">
-        <v>193</v>
+      <c r="K36" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="N36" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9" t="s">
-        <v>200</v>
+        <v>218</v>
+      </c>
+      <c r="O36" s="3"/>
+    </row>
+    <row r="37" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>219</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>18</v>
+        <v>190</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>2.88</v>
+        <v>1.99</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
-      <c r="K37" s="3" t="s">
-        <v>202</v>
+      <c r="K37" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="N37" s="5" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="9" t="s">
-        <v>207</v>
+      <c r="A38" s="6" t="s">
+        <v>224</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>18</v>
+        <v>225</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>2.90666666666667</v>
+        <v>3.50666666666667</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="3" t="s">
-        <v>208</v>
+      <c r="K38" s="2" t="s">
+        <v>226</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="N38" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="O38" s="3"/>
-    </row>
-    <row r="39" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="9" t="s">
-        <v>212</v>
+        <v>229</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>224</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>18</v>
+        <v>231</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>1.99</v>
+        <v>5.45</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="3" t="s">
-        <v>213</v>
+      <c r="K39" s="2" t="s">
+        <v>226</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="N39" s="5" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="9" t="s">
-        <v>217</v>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>233</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>3.50666666666667</v>
+        <v>3.30666666666667</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="3" t="s">
-        <v>219</v>
+      <c r="K40" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="N40" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="O40" s="3" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="9" t="s">
-        <v>217</v>
+        <v>237</v>
+      </c>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>238</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>224</v>
+        <v>18</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>5.45</v>
+        <v>2.4</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="3" t="s">
-        <v>219</v>
+      <c r="K41" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="N41" s="5" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="9" t="s">
-        <v>225</v>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>244</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>18</v>
+        <v>190</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>3.30666666666667</v>
+        <v>3.56</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="3" t="s">
-        <v>226</v>
+      <c r="K42" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="N42" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9" t="s">
-        <v>230</v>
+        <v>242</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3" t="s">
-        <v>201</v>
+        <v>247</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>18</v>
+        <v>225</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>2.4</v>
+        <v>5.09333333333333</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
-      <c r="K43" s="3" t="s">
-        <v>231</v>
+      <c r="K43" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="N43" s="5" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9" t="s">
-        <v>236</v>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3" t="s">
-        <v>201</v>
+        <v>247</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>18</v>
+        <v>204</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>3.56</v>
+        <v>8.58666666666667</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="3" t="s">
-        <v>231</v>
+      <c r="K44" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="N44" s="5" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9" t="s">
-        <v>237</v>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>254</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>5.09333333333333</v>
+        <v>2.18666666666667</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
-      <c r="K45" s="3" t="s">
-        <v>240</v>
+      <c r="K45" s="2" t="s">
+        <v>257</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="N45" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>244</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="O45" s="3"/>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9" t="s">
-        <v>237</v>
+      <c r="A46" s="6" t="s">
+        <v>261</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3" t="s">
-        <v>238</v>
+        <v>17</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>245</v>
+        <v>18</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>8.58666666666667</v>
+        <v>3.12</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
-      <c r="K46" s="3" t="s">
-        <v>240</v>
+      <c r="K46" s="2" t="s">
+        <v>262</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="N46" s="5" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9" t="s">
-        <v>246</v>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="43.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3" t="s">
-        <v>247</v>
+        <v>17</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>248</v>
+        <v>18</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>2.18666666666667</v>
+        <v>2.4</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
-      <c r="K47" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>250</v>
-      </c>
+      <c r="K47" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="N47" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9" t="s">
-        <v>253</v>
+        <v>269</v>
+      </c>
+      <c r="N47" s="5"/>
+      <c r="O47" s="10" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="s">
+        <v>271</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>16</v>
@@ -4333,31 +4449,31 @@
         <v>18</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>3.12</v>
+        <v>2.42666666666667</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
-      <c r="K48" s="3" t="s">
-        <v>254</v>
+      <c r="K48" s="2" t="s">
+        <v>272</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="N48" s="5" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="9" t="s">
-        <v>259</v>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="11" t="s">
+        <v>275</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>16</v>
@@ -4370,267 +4486,267 @@
         <v>18</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>2.4</v>
+        <v>3.53333333333333</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="5"/>
-      <c r="O49" s="3"/>
+      <c r="K49" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="N49" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9" t="s">
-        <v>230</v>
+      <c r="A50" s="6" t="s">
+        <v>277</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3" t="s">
-        <v>17</v>
+        <v>278</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>18</v>
+        <v>231</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>2.42666666666667</v>
+        <v>4.42666666666667</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
-      <c r="K50" s="3" t="s">
-        <v>260</v>
+      <c r="K50" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="N50" s="5" t="s">
-        <v>234</v>
+        <v>282</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="9" t="s">
-        <v>236</v>
+        <v>283</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="6" t="s">
+        <v>284</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3" t="s">
-        <v>17</v>
+        <v>278</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>3.53333333333333</v>
+        <v>2.36</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
-      <c r="K51" s="3" t="s">
-        <v>260</v>
+      <c r="K51" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="N51" s="5" t="s">
-        <v>234</v>
+        <v>288</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="9" t="s">
-        <v>263</v>
+        <v>289</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6" t="s">
+        <v>290</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="3" t="s">
-        <v>264</v>
+        <v>17</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>4.42666666666667</v>
+        <v>1.6</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
-      <c r="K52" s="3" t="s">
-        <v>266</v>
+      <c r="K52" s="2" t="s">
+        <v>292</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="N52" s="5" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>270</v>
+        <v>296</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="9" t="s">
-        <v>271</v>
+      <c r="A53" s="6" t="s">
+        <v>297</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F53" s="7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="M53" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="N53" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="O53" s="3" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="9" t="s">
-        <v>277</v>
+      <c r="D53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F53" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6" t="s">
+        <v>301</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="F54" s="7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="N54" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>283</v>
+      <c r="D54" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="F54" s="1" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="9" t="s">
-        <v>284</v>
+      <c r="A55" s="6" t="s">
+        <v>307</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>285</v>
+        <v>9.51</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>309</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="9" t="s">
-        <v>288</v>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
+        <v>314</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>247</v>
+        <v>16</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>248</v>
+        <v>308</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>289</v>
+        <v>9.51</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>315</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="9" t="s">
-        <v>293</v>
+        <v>318</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="124.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6" t="s">
+        <v>320</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>16</v>
@@ -4639,30 +4755,30 @@
         <v>16</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>9.51</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>295</v>
+      <c r="K57" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
-        <v>300</v>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6" t="s">
+        <v>326</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>16</v>
@@ -4671,30 +4787,30 @@
         <v>16</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>9.51</v>
       </c>
-      <c r="K58" s="1" t="s">
-        <v>301</v>
+      <c r="K58" s="2" t="s">
+        <v>327</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
-        <v>306</v>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="113.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="6" t="s">
+        <v>332</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>16</v>
@@ -4703,179 +4819,179 @@
         <v>16</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>294</v>
+        <v>225</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>307</v>
+        <v>7.56</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
-        <v>312</v>
+        <v>337</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="6" t="s">
+        <v>338</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>16</v>
+        <v>247</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>313</v>
+        <v>7.81333333333333</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>314</v>
+        <v>249</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>315</v>
+        <v>250</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>316</v>
+        <v>251</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
-        <v>318</v>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6" t="s">
+        <v>339</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>16</v>
+        <v>247</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>239</v>
+        <v>18</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>319</v>
+        <v>6.52</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>320</v>
+        <v>249</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>322</v>
+        <v>251</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
-        <v>324</v>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="57.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6" t="s">
+        <v>341</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>238</v>
+        <v>342</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>18</v>
+        <v>343</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>7.81333333333333</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>240</v>
+        <v>8.6</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>241</v>
+        <v>157</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>242</v>
+        <v>344</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>243</v>
+        <v>159</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
-        <v>325</v>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="57.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="6" t="s">
+        <v>345</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>238</v>
+        <v>342</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>18</v>
+        <v>343</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>240</v>
+        <v>8.6</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>241</v>
+        <v>163</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>242</v>
+        <v>346</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>243</v>
+        <v>159</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
-        <v>326</v>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="57.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="6" t="s">
+        <v>347</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="F64" s="1" t="n">
         <v>8.6</v>
       </c>
-      <c r="K64" s="1" t="s">
-        <v>156</v>
+      <c r="K64" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>158</v>
+        <v>348</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>159</v>
@@ -4884,2671 +5000,2836 @@
         <v>160</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
-        <v>329</v>
+    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="6" t="s">
+        <v>349</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="F65" s="1" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>162</v>
+        <v>350</v>
+      </c>
+      <c r="F65" s="12" t="n">
+        <v>5.74666666666667</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>351</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>163</v>
+        <v>352</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>164</v>
+        <v>353</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>159</v>
+        <v>354</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="s">
-        <v>330</v>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="6" t="s">
+        <v>356</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="F66" s="1" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>166</v>
+        <v>350</v>
+      </c>
+      <c r="F66" s="12" t="n">
+        <v>5.74666666666667</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>357</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>167</v>
+        <v>358</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>168</v>
+        <v>359</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>159</v>
+        <v>360</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
-        <v>331</v>
+        <v>361</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="6" t="s">
+        <v>362</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="F67" s="10" t="n">
+        <v>350</v>
+      </c>
+      <c r="F67" s="12" t="n">
         <v>5.74666666666667</v>
       </c>
-      <c r="K67" s="1" t="s">
-        <v>333</v>
+      <c r="K67" s="2" t="s">
+        <v>363</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
-        <v>338</v>
+        <v>367</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="6" t="s">
+        <v>368</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="F68" s="10" t="n">
-        <v>5.74666666666667</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>339</v>
+        <v>190</v>
+      </c>
+      <c r="F68" s="12" t="n">
+        <v>2.70666666666667</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>369</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
-        <v>344</v>
+        <v>373</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="57.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="6" t="s">
+        <v>374</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="F69" s="10" t="n">
-        <v>5.74666666666667</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>346</v>
+        <v>375</v>
+      </c>
+      <c r="F69" s="12" t="n">
+        <v>6.82666666666667</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>376</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>347</v>
+        <v>377</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="O69" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
-        <v>350</v>
+        <v>378</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="6" t="s">
+        <v>379</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="F70" s="10" t="n">
-        <v>2.70666666666667</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="L70" s="1" t="s">
-        <v>353</v>
+        <v>375</v>
+      </c>
+      <c r="F70" s="12" t="n">
+        <v>8.69333333333333</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>380</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="N70" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="O70" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
-        <v>357</v>
+        <v>381</v>
+      </c>
+      <c r="N70" s="13" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="6" t="s">
+        <v>383</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="F71" s="10" t="n">
-        <v>6.82666666666667</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B72" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="F71" s="12" t="n">
+        <v>12.4133333333333</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="N71" s="13" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="72" s="14" customFormat="true" ht="35.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="F72" s="10" t="n">
-        <v>8.69333333333333</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
-        <v>360</v>
+      <c r="D72" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F72" s="15" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="L72" s="6"/>
+      <c r="M72" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="N72" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="O72" s="17" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="6" t="s">
+        <v>393</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>327</v>
+        <v>388</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="F73" s="10" t="n">
-        <v>12.4133333333333</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
-        <v>361</v>
+        <v>343</v>
+      </c>
+      <c r="F73" s="12" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="K73" s="2"/>
+      <c r="M73" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="N73" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="O73" s="18" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="6" t="s">
+        <v>397</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>327</v>
+        <v>388</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F74" s="10" t="n">
-        <v>6.85333333333333</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>225</v>
+      </c>
+      <c r="F74" s="12" t="n">
+        <v>3.53333333333333</v>
+      </c>
+      <c r="K74" s="2"/>
+      <c r="M74" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="N74" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="O74" s="18" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>16</v>
+        <v>401</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>402</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>327</v>
+        <v>403</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F75" s="10" t="n">
-        <v>6.85333333333333</v>
+        <v>404</v>
+      </c>
+      <c r="F75" s="12" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="H75" s="12" t="n">
+        <v>9.36</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>16</v>
+        <v>411</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>402</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>327</v>
+        <v>403</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F76" s="10" t="n">
-        <v>6.85333333333333</v>
+        <v>412</v>
+      </c>
+      <c r="F76" s="12" t="n">
+        <v>7.20583244619216</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>16</v>
+        <v>417</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>402</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>327</v>
+        <v>403</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F77" s="10" t="n">
-        <v>6.85333333333333</v>
+        <v>343</v>
+      </c>
+      <c r="F77" s="12" t="n">
+        <v>7.12887282217288</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>16</v>
+        <v>422</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>402</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>366</v>
+        <v>423</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="F78" s="10" t="n">
-        <v>4.28</v>
+        <v>225</v>
+      </c>
+      <c r="F78" s="12" t="n">
+        <v>9.41425446816473</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>16</v>
+        <v>428</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>402</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>366</v>
+        <v>423</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="F79" s="10" t="n">
-        <v>5.12</v>
+        <v>308</v>
+      </c>
+      <c r="F79" s="12" t="n">
+        <v>16.1425471275276</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>16</v>
+        <v>432</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>402</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>366</v>
+        <v>423</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="F80" s="10" t="n">
-        <v>3.53333333333333</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>433</v>
+      </c>
+      <c r="F80" s="12" t="n">
+        <v>8.17421149404765</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="O80" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>370</v>
+        <v>438</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="F81" s="10" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="H81" s="10" t="n">
-        <v>9.36</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="L81" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="M81" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="N81" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="O81" s="1" t="s">
-        <v>379</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="F81" s="12" t="n">
+        <v>47.5739038023044</v>
+      </c>
+      <c r="K81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>380</v>
+        <v>439</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>372</v>
+        <v>423</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="F82" s="10" t="n">
-        <v>7.20583244619216</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>382</v>
+        <v>225</v>
+      </c>
+      <c r="F82" s="12" t="n">
+        <v>4.43564063414339</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>440</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>383</v>
+        <v>441</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>384</v>
+        <v>442</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>385</v>
+        <v>443</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>386</v>
+        <v>444</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>372</v>
+        <v>423</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="F83" s="10" t="n">
-        <v>7.12887282217288</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>388</v>
+        <v>225</v>
+      </c>
+      <c r="F83" s="12" t="n">
+        <v>4.43564063414339</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>445</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>389</v>
+        <v>446</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>390</v>
+        <v>447</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>391</v>
+        <v>448</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>392</v>
+        <v>449</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>393</v>
+        <v>450</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F84" s="10" t="n">
-        <v>9.41425446816473</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>394</v>
+        <v>451</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>9.10322409828036</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>452</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>395</v>
+        <v>453</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>396</v>
+        <v>454</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>397</v>
+        <v>455</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>398</v>
+        <v>456</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>393</v>
+        <v>450</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="F85" s="10" t="n">
-        <v>16.1425471275276</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>400</v>
+        <v>451</v>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>8.69874275637259</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>457</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>401</v>
+        <v>458</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>402</v>
+        <v>459</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>397</v>
+        <v>460</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>403</v>
+        <v>461</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>393</v>
+        <v>450</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="F86" s="10" t="n">
-        <v>8.17421149404765</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>405</v>
+        <v>462</v>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>6.1526914161219</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>463</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>406</v>
+        <v>464</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>407</v>
+        <v>465</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>408</v>
+        <v>466</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>409</v>
+        <v>467</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="F87" s="10" t="n">
-        <v>47.5739038023044</v>
+        <v>468</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="F87" s="12" t="n">
+        <v>12.8384257580547</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="O87" s="1" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>410</v>
+        <v>473</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>393</v>
+        <v>468</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="F88" s="10" t="n">
-        <v>4.43564063414339</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>411</v>
+        <v>256</v>
+      </c>
+      <c r="F88" s="12" t="n">
+        <v>9.9453468044268</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>469</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>413</v>
+        <v>471</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>414</v>
+        <v>472</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>415</v>
+        <v>474</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>393</v>
+        <v>468</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="F89" s="10" t="n">
-        <v>4.43564063414339</v>
-      </c>
-      <c r="K89" s="1" t="s">
-        <v>416</v>
+        <v>451</v>
+      </c>
+      <c r="F89" s="12" t="n">
+        <v>10.0912863679472</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>475</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>417</v>
+        <v>476</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>418</v>
+        <v>477</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>419</v>
+        <v>460</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>420</v>
+        <v>478</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>421</v>
+        <v>468</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="F90" s="10" t="n">
-        <v>9.10322409828036</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>423</v>
+        <v>225</v>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>21.7676927338399</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>479</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>424</v>
+        <v>480</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>425</v>
+        <v>481</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>426</v>
+        <v>482</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>427</v>
+        <v>483</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>421</v>
+        <v>468</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="F91" s="10" t="n">
-        <v>8.69874275637259</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>428</v>
+        <v>433</v>
+      </c>
+      <c r="F91" s="12" t="n">
+        <v>11.2449714229459</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>484</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>429</v>
+        <v>485</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>430</v>
+        <v>486</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>431</v>
+        <v>487</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>432</v>
+        <v>488</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>421</v>
+        <v>468</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="F92" s="10" t="n">
-        <v>6.1526914161219</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>434</v>
+        <v>489</v>
+      </c>
+      <c r="F92" s="12" t="n">
+        <v>4.3868758954215</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>490</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>435</v>
+        <v>491</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>436</v>
+        <v>492</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>437</v>
+        <v>493</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>438</v>
+        <v>494</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>439</v>
+        <v>468</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="F93" s="10" t="n">
-        <v>12.8384257580547</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>440</v>
+        <v>489</v>
+      </c>
+      <c r="F93" s="12" t="n">
+        <v>4.3868758954215</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>495</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>441</v>
+        <v>496</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>442</v>
+        <v>497</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>443</v>
+        <v>498</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>444</v>
+        <v>499</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>439</v>
+        <v>468</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="F94" s="10" t="n">
-        <v>9.9453468044268</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>440</v>
+        <v>489</v>
+      </c>
+      <c r="F94" s="12" t="n">
+        <v>4.3868758954215</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>500</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>441</v>
+        <v>501</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>442</v>
+        <v>502</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>443</v>
+        <v>503</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>445</v>
+        <v>504</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>439</v>
+        <v>505</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="F95" s="10" t="n">
-        <v>10.0912863679472</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>447</v>
+        <v>489</v>
+      </c>
+      <c r="F95" s="12" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>506</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>448</v>
+        <v>507</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>449</v>
+        <v>508</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>431</v>
+        <v>509</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>450</v>
+        <v>510</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>439</v>
+        <v>511</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F96" s="10" t="n">
-        <v>21.7676927338399</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>451</v>
+        <v>256</v>
+      </c>
+      <c r="F96" s="12" t="n">
+        <v>3.15658586904879</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>512</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>452</v>
+        <v>513</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="O96" s="1" t="s">
-        <v>454</v>
+        <v>514</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>455</v>
+        <v>515</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>439</v>
+        <v>511</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="F97" s="10" t="n">
-        <v>11.2449714229459</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>457</v>
+        <v>256</v>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>3.15658586904879</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>512</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>458</v>
+        <v>513</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="O97" s="1" t="s">
-        <v>460</v>
+        <v>514</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>461</v>
+        <v>516</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>439</v>
+        <v>511</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="F98" s="10" t="n">
-        <v>4.3868758954215</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>463</v>
+        <v>256</v>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>3.15658586904879</v>
+      </c>
+      <c r="K98" s="2" t="s">
+        <v>512</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>464</v>
+        <v>513</v>
       </c>
       <c r="M98" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="O98" s="1" t="s">
-        <v>466</v>
+        <v>514</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>467</v>
+        <v>517</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>439</v>
+        <v>518</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="F99" s="10" t="n">
-        <v>4.3868758954215</v>
-      </c>
-      <c r="K99" s="1" t="s">
-        <v>468</v>
+        <v>225</v>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>6.96608725800308</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>519</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>469</v>
+        <v>520</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>470</v>
+        <v>521</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>471</v>
+        <v>522</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>472</v>
+        <v>523</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>439</v>
+        <v>518</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="F100" s="10" t="n">
-        <v>4.3868758954215</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="L100" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="M100" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="O100" s="1" t="s">
-        <v>476</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="F100" s="12" t="n">
+        <v>13.6358622308997</v>
+      </c>
+      <c r="K100" s="2"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>477</v>
+        <v>524</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>478</v>
+        <v>518</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="F101" s="10" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>479</v>
+        <v>190</v>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>8.42424160894899</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>525</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>480</v>
+        <v>526</v>
       </c>
       <c r="M101" s="1" t="s">
-        <v>481</v>
+        <v>527</v>
       </c>
       <c r="O101" s="1" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>483</v>
+        <v>528</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>484</v>
+        <v>518</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="F102" s="10" t="n">
-        <v>3.15658586904879</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>485</v>
+        <v>433</v>
+      </c>
+      <c r="F102" s="12" t="n">
+        <v>7.60694458797006</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>486</v>
+        <v>530</v>
       </c>
       <c r="M102" s="1" t="s">
-        <v>487</v>
+        <v>531</v>
+      </c>
+      <c r="O102" s="1" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>488</v>
+        <v>533</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>484</v>
+        <v>518</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="F103" s="10" t="n">
-        <v>3.15658586904879</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>485</v>
+        <v>433</v>
+      </c>
+      <c r="F103" s="12" t="n">
+        <v>9.74337212295685</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>534</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>486</v>
+        <v>535</v>
       </c>
       <c r="M103" s="1" t="s">
-        <v>487</v>
+        <v>536</v>
+      </c>
+      <c r="O103" s="1" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>489</v>
+        <v>538</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>484</v>
+        <v>539</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="F104" s="10" t="n">
-        <v>3.15658586904879</v>
-      </c>
-      <c r="K104" s="1" t="s">
-        <v>485</v>
+        <v>404</v>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>14.0873350483031</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>540</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>486</v>
+        <v>541</v>
       </c>
       <c r="M104" s="1" t="s">
-        <v>487</v>
+        <v>542</v>
+      </c>
+      <c r="O104" s="1" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>490</v>
+        <v>544</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>491</v>
+        <v>539</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F105" s="10" t="n">
-        <v>6.96608725800308</v>
-      </c>
-      <c r="K105" s="1" t="s">
-        <v>492</v>
+        <v>256</v>
+      </c>
+      <c r="F105" s="12" t="n">
+        <v>10.1019259473047</v>
+      </c>
+      <c r="K105" s="2" t="s">
+        <v>545</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>493</v>
+        <v>546</v>
       </c>
       <c r="M105" s="1" t="s">
-        <v>494</v>
+        <v>547</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>495</v>
+        <v>548</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>496</v>
+        <v>549</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>491</v>
+        <v>539</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="F106" s="10" t="n">
-        <v>13.6358622308997</v>
+        <v>256</v>
+      </c>
+      <c r="F106" s="12" t="n">
+        <v>11.4703531790024</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="M106" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="O106" s="1" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>497</v>
+        <v>553</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>491</v>
+        <v>539</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="F107" s="10" t="n">
-        <v>8.42424160894899</v>
-      </c>
-      <c r="K107" s="1" t="s">
-        <v>498</v>
+        <v>404</v>
+      </c>
+      <c r="F107" s="12" t="n">
+        <v>15.3202849695152</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>554</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>499</v>
+        <v>555</v>
       </c>
       <c r="M107" s="1" t="s">
-        <v>500</v>
+        <v>556</v>
       </c>
       <c r="O107" s="1" t="s">
-        <v>443</v>
+        <v>557</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>501</v>
+        <v>558</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>491</v>
+        <v>559</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="F108" s="10" t="n">
-        <v>7.60694458797006</v>
-      </c>
-      <c r="K108" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="L108" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="M108" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="O108" s="1" t="s">
-        <v>505</v>
-      </c>
+      <c r="F108" s="12" t="n">
+        <v>15.3663898133977</v>
+      </c>
+      <c r="K108" s="2"/>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>506</v>
+        <v>560</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>491</v>
+        <v>559</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="F109" s="10" t="n">
-        <v>9.74337212295685</v>
-      </c>
-      <c r="K109" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="L109" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="M109" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="O109" s="1" t="s">
-        <v>510</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="F109" s="12" t="n">
+        <v>10.5750325760684</v>
+      </c>
+      <c r="K109" s="2"/>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>511</v>
+        <v>562</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>512</v>
+        <v>559</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="F110" s="10" t="n">
-        <v>14.0873350483031</v>
-      </c>
-      <c r="K110" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="L110" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="M110" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="O110" s="1" t="s">
-        <v>516</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="F110" s="12" t="n">
+        <v>8.68828050333771</v>
+      </c>
+      <c r="K110" s="2"/>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>517</v>
+        <v>563</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>512</v>
+        <v>559</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="F111" s="10" t="n">
-        <v>10.1019259473047</v>
-      </c>
-      <c r="K111" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="L111" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="M111" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="O111" s="1" t="s">
-        <v>521</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="F111" s="12" t="n">
+        <v>6.43907342716138</v>
+      </c>
+      <c r="K111" s="2"/>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>522</v>
+        <v>564</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>512</v>
+        <v>565</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="F112" s="10" t="n">
-        <v>11.4703531790024</v>
-      </c>
-      <c r="K112" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="L112" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="M112" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="O112" s="1" t="s">
-        <v>521</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="F112" s="12" t="n">
+        <v>9.73681104901972</v>
+      </c>
+      <c r="K112" s="2"/>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>526</v>
+        <v>566</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>512</v>
+        <v>565</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="F113" s="10" t="n">
-        <v>15.3202849695152</v>
-      </c>
-      <c r="K113" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="L113" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="M113" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="O113" s="1" t="s">
-        <v>530</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="F113" s="12" t="n">
+        <v>8.88404876351578</v>
+      </c>
+      <c r="K113" s="2"/>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>531</v>
+        <v>567</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>371</v>
+        <v>568</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>532</v>
+        <v>568</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="F114" s="10" t="n">
-        <v>15.3663898133977</v>
+        <v>569</v>
+      </c>
+      <c r="F114" s="12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="M114" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="O114" s="1" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>533</v>
+        <v>567</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>371</v>
+        <v>568</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>532</v>
+        <v>568</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="F115" s="10" t="n">
-        <v>10.5750325760684</v>
+        <v>574</v>
+      </c>
+      <c r="F115" s="12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="M115" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="O115" s="1" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>535</v>
+        <v>575</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>371</v>
+        <v>568</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>532</v>
+        <v>568</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="F116" s="10" t="n">
-        <v>8.68828050333771</v>
+        <v>569</v>
+      </c>
+      <c r="F116" s="12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="M116" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="O116" s="1" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>536</v>
+        <v>575</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>371</v>
+        <v>568</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>532</v>
+        <v>568</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="F117" s="10" t="n">
-        <v>6.43907342716138</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>574</v>
+      </c>
+      <c r="F117" s="12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="L117" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="M117" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="O117" s="1" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>537</v>
+        <v>579</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>371</v>
+        <v>568</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>538</v>
+        <v>568</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="F118" s="10" t="n">
-        <v>9.73681104901972</v>
+        <v>580</v>
+      </c>
+      <c r="F118" s="12" t="n">
+        <v>4.52562911343399</v>
+      </c>
+      <c r="K118" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="L118" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="M118" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="O118" s="1" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>371</v>
+        <v>568</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>538</v>
+        <v>568</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="F119" s="10" t="n">
-        <v>8.88404876351578</v>
+        <v>433</v>
+      </c>
+      <c r="F119" s="12" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="K119" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="M119" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="O119" s="1" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>541</v>
+        <v>590</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="F120" s="10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K120" s="1" t="s">
-        <v>544</v>
+        <v>489</v>
+      </c>
+      <c r="F120" s="12" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>591</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>545</v>
+        <v>592</v>
       </c>
       <c r="M120" s="1" t="s">
-        <v>546</v>
+        <v>593</v>
       </c>
       <c r="O120" s="1" t="s">
-        <v>547</v>
+        <v>594</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>541</v>
+        <v>595</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="F121" s="10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="K121" s="1" t="s">
-        <v>544</v>
+        <v>596</v>
+      </c>
+      <c r="F121" s="12" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="K121" s="2" t="s">
+        <v>597</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>545</v>
+        <v>598</v>
       </c>
       <c r="M121" s="1" t="s">
-        <v>546</v>
+        <v>599</v>
       </c>
       <c r="O121" s="1" t="s">
-        <v>547</v>
+        <v>600</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>549</v>
+        <v>601</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="F122" s="10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>550</v>
+        <v>596</v>
+      </c>
+      <c r="F122" s="12" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="K122" s="2" t="s">
+        <v>602</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>551</v>
+        <v>603</v>
       </c>
       <c r="M122" s="1" t="s">
-        <v>552</v>
+        <v>604</v>
       </c>
       <c r="O122" s="1" t="s">
-        <v>547</v>
+        <v>605</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>549</v>
+        <v>606</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>542</v>
+        <v>607</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>542</v>
+        <v>607</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="F123" s="10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="K123" s="1" t="s">
-        <v>550</v>
+        <v>404</v>
+      </c>
+      <c r="F123" s="12" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K123" s="2" t="s">
+        <v>608</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>551</v>
+        <v>609</v>
       </c>
       <c r="M123" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="O123" s="1" t="s">
-        <v>547</v>
+        <v>610</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>553</v>
+        <v>611</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>542</v>
+        <v>607</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>542</v>
+        <v>607</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="F124" s="10" t="n">
-        <v>4.52562911343399</v>
-      </c>
-      <c r="K124" s="1" t="s">
-        <v>555</v>
+        <v>404</v>
+      </c>
+      <c r="F124" s="12" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>612</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>556</v>
+        <v>613</v>
       </c>
       <c r="M124" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="O124" s="1" t="s">
-        <v>558</v>
+        <v>614</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>559</v>
+        <v>615</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>542</v>
+        <v>607</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>542</v>
+        <v>607</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="F125" s="10" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="K125" s="1" t="s">
-        <v>560</v>
+      <c r="F125" s="12" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>616</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>561</v>
+        <v>617</v>
       </c>
       <c r="M125" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="O125" s="1" t="s">
-        <v>563</v>
+        <v>618</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>564</v>
+        <v>619</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>542</v>
+        <v>607</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>542</v>
+        <v>607</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="F126" s="10" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="K126" s="1" t="s">
-        <v>565</v>
+        <v>404</v>
+      </c>
+      <c r="F126" s="12" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>608</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>566</v>
+        <v>609</v>
       </c>
       <c r="M126" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="O126" s="1" t="s">
-        <v>568</v>
+        <v>610</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>569</v>
+        <v>620</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>542</v>
+        <v>607</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>542</v>
+        <v>607</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="F127" s="10" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="K127" s="1" t="s">
-        <v>571</v>
+        <v>404</v>
+      </c>
+      <c r="F127" s="12" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K127" s="2" t="s">
+        <v>612</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>572</v>
+        <v>613</v>
       </c>
       <c r="M127" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="O127" s="1" t="s">
-        <v>574</v>
+        <v>614</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>575</v>
+        <v>621</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>542</v>
+        <v>607</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>542</v>
+        <v>607</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="F128" s="10" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="K128" s="1" t="s">
-        <v>576</v>
+        <v>404</v>
+      </c>
+      <c r="F128" s="12" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K128" s="2" t="s">
+        <v>616</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>577</v>
+        <v>617</v>
       </c>
       <c r="M128" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="O128" s="1" t="s">
-        <v>579</v>
+        <v>618</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>580</v>
+        <v>622</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="F129" s="10" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="K129" s="1" t="s">
-        <v>583</v>
+        <v>623</v>
+      </c>
+      <c r="F129" s="12" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="K129" s="2" t="s">
+        <v>624</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>584</v>
+        <v>625</v>
       </c>
       <c r="M129" s="1" t="s">
-        <v>585</v>
+        <v>626</v>
+      </c>
+      <c r="O129" s="1" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>586</v>
+        <v>628</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="F130" s="10" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="K130" s="1" t="s">
-        <v>587</v>
+        <v>623</v>
+      </c>
+      <c r="F130" s="12" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="K130" s="2" t="s">
+        <v>629</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>588</v>
+        <v>630</v>
       </c>
       <c r="M130" s="1" t="s">
-        <v>589</v>
+        <v>631</v>
+      </c>
+      <c r="O130" s="1" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>590</v>
+        <v>633</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="F131" s="10" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="K131" s="1" t="s">
-        <v>591</v>
+        <v>623</v>
+      </c>
+      <c r="F131" s="12" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="K131" s="2" t="s">
+        <v>634</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>592</v>
+        <v>635</v>
       </c>
       <c r="M131" s="1" t="s">
-        <v>593</v>
+        <v>636</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>594</v>
+        <v>637</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="F132" s="10" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="K132" s="1" t="s">
-        <v>583</v>
+        <v>623</v>
+      </c>
+      <c r="F132" s="12" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="K132" s="2" t="s">
+        <v>624</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>584</v>
+        <v>625</v>
       </c>
       <c r="M132" s="1" t="s">
-        <v>585</v>
+        <v>626</v>
+      </c>
+      <c r="O132" s="1" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>595</v>
+        <v>638</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="F133" s="10" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="K133" s="1" t="s">
-        <v>587</v>
+        <v>639</v>
+      </c>
+      <c r="F133" s="12" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>640</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>588</v>
+        <v>641</v>
       </c>
       <c r="M133" s="1" t="s">
-        <v>589</v>
+        <v>642</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>596</v>
+        <v>643</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="F134" s="10" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="K134" s="1" t="s">
-        <v>591</v>
+        <v>639</v>
+      </c>
+      <c r="F134" s="12" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="K134" s="2" t="s">
+        <v>644</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>592</v>
+        <v>645</v>
       </c>
       <c r="M134" s="1" t="s">
-        <v>593</v>
+        <v>646</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>597</v>
+        <v>647</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="F135" s="10" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="K135" s="1" t="s">
-        <v>599</v>
+        <v>639</v>
+      </c>
+      <c r="F135" s="12" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="K135" s="2" t="s">
+        <v>648</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>600</v>
+        <v>649</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="O135" s="1" t="s">
-        <v>602</v>
+        <v>650</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>603</v>
+        <v>651</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="F136" s="10" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="K136" s="1" t="s">
-        <v>604</v>
+        <v>652</v>
+      </c>
+      <c r="F136" s="12" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="K136" s="2" t="s">
+        <v>653</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>605</v>
+        <v>654</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>606</v>
+        <v>655</v>
       </c>
       <c r="O136" s="1" t="s">
-        <v>607</v>
+        <v>656</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>608</v>
+        <v>657</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="F137" s="10" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="K137" s="1" t="s">
-        <v>609</v>
+        <v>652</v>
+      </c>
+      <c r="F137" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="K137" s="2" t="s">
+        <v>658</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>610</v>
+        <v>659</v>
       </c>
       <c r="M137" s="1" t="s">
-        <v>611</v>
+        <v>660</v>
+      </c>
+      <c r="O137" s="1" t="s">
+        <v>661</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>612</v>
+        <v>662</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="F138" s="10" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="K138" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="L138" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="M138" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="O138" s="1" t="s">
-        <v>602</v>
-      </c>
+        <v>663</v>
+      </c>
+      <c r="F138" s="12" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="K138" s="2"/>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>613</v>
+        <v>664</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="F139" s="10" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="K139" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="L139" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="M139" s="1" t="s">
-        <v>617</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="F139" s="12" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="K139" s="2"/>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>618</v>
+        <v>665</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="F140" s="10" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="K140" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="L140" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="M140" s="1" t="s">
-        <v>621</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="F140" s="12" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="K140" s="2"/>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>622</v>
+        <v>666</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="F141" s="10" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="K141" s="1" t="s">
-        <v>623</v>
+        <v>404</v>
+      </c>
+      <c r="F141" s="12" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K141" s="2" t="s">
+        <v>667</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>624</v>
+        <v>668</v>
       </c>
       <c r="M141" s="1" t="s">
-        <v>625</v>
+        <v>669</v>
+      </c>
+      <c r="N141" s="1"/>
+      <c r="O141" s="1" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>626</v>
+        <v>671</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="F142" s="10" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="K142" s="1" t="s">
-        <v>628</v>
+        <v>404</v>
+      </c>
+      <c r="F142" s="12" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K142" s="2" t="s">
+        <v>672</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>629</v>
+        <v>673</v>
       </c>
       <c r="M142" s="1" t="s">
-        <v>630</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="N142" s="1"/>
       <c r="O142" s="1" t="s">
-        <v>631</v>
+        <v>675</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>632</v>
+        <v>676</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="F143" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="K143" s="1" t="s">
-        <v>633</v>
+        <v>404</v>
+      </c>
+      <c r="F143" s="12" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K143" s="2" t="s">
+        <v>677</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>634</v>
+        <v>678</v>
       </c>
       <c r="M143" s="1" t="s">
-        <v>635</v>
-      </c>
+        <v>679</v>
+      </c>
+      <c r="N143" s="1"/>
       <c r="O143" s="1" t="s">
-        <v>636</v>
+        <v>680</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>637</v>
+        <v>681</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="F144" s="10" t="n">
-        <v>10.56</v>
+        <v>404</v>
+      </c>
+      <c r="F144" s="12" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K144" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="L144" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="M144" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="N144" s="1"/>
+      <c r="O144" s="1" t="s">
+        <v>685</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>639</v>
+        <v>686</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="F145" s="10" t="n">
-        <v>13.33</v>
+        <v>404</v>
+      </c>
+      <c r="F145" s="12" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K145" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="L145" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="M145" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="N145" s="1"/>
+      <c r="O145" s="1" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>640</v>
+        <v>691</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="F146" s="10" t="n">
-        <v>7.78</v>
+        <v>404</v>
+      </c>
+      <c r="F146" s="12" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K146" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="L146" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="M146" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="N146" s="1"/>
+      <c r="O146" s="1" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>641</v>
+        <v>696</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="F147" s="10" t="n">
+        <v>404</v>
+      </c>
+      <c r="F147" s="12" t="n">
         <v>3.89</v>
       </c>
-      <c r="K147" s="1" t="s">
-        <v>642</v>
+      <c r="K147" s="2" t="s">
+        <v>697</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>643</v>
+        <v>698</v>
       </c>
       <c r="M147" s="1" t="s">
-        <v>644</v>
+        <v>699</v>
       </c>
       <c r="N147" s="1"/>
       <c r="O147" s="1" t="s">
-        <v>645</v>
+        <v>700</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>646</v>
+        <v>701</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="F148" s="10" t="n">
+        <v>404</v>
+      </c>
+      <c r="F148" s="12" t="n">
         <v>3.89</v>
       </c>
-      <c r="K148" s="1" t="s">
-        <v>647</v>
+      <c r="K148" s="2" t="s">
+        <v>702</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>648</v>
+        <v>703</v>
       </c>
       <c r="M148" s="1" t="s">
-        <v>649</v>
+        <v>704</v>
       </c>
       <c r="N148" s="1"/>
       <c r="O148" s="1" t="s">
-        <v>650</v>
+        <v>705</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>651</v>
+        <v>706</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="F149" s="10" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="K149" s="1" t="s">
-        <v>652</v>
+        <v>561</v>
+      </c>
+      <c r="F149" s="12" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="K149" s="2" t="s">
+        <v>707</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>653</v>
+        <v>708</v>
       </c>
       <c r="M149" s="1" t="s">
-        <v>654</v>
+        <v>709</v>
       </c>
       <c r="N149" s="1"/>
       <c r="O149" s="1" t="s">
-        <v>655</v>
+        <v>710</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>656</v>
+        <v>711</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="F150" s="10" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="K150" s="1" t="s">
-        <v>657</v>
+        <v>712</v>
+      </c>
+      <c r="F150" s="12" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="K150" s="2" t="s">
+        <v>713</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>658</v>
+        <v>714</v>
       </c>
       <c r="M150" s="1" t="s">
-        <v>659</v>
+        <v>715</v>
       </c>
       <c r="N150" s="1"/>
-      <c r="O150" s="1" t="s">
-        <v>660</v>
-      </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>661</v>
+        <v>716</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="F151" s="10" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="K151" s="1" t="s">
-        <v>662</v>
+        <v>712</v>
+      </c>
+      <c r="F151" s="12" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="K151" s="2" t="s">
+        <v>717</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>663</v>
+        <v>718</v>
       </c>
       <c r="M151" s="1" t="s">
-        <v>664</v>
+        <v>719</v>
       </c>
       <c r="N151" s="1"/>
-      <c r="O151" s="1" t="s">
-        <v>665</v>
-      </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>666</v>
+        <v>711</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="F152" s="10" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="K152" s="1" t="s">
-        <v>667</v>
+        <v>149</v>
+      </c>
+      <c r="F152" s="12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K152" s="2" t="s">
+        <v>713</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="M152" s="1" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="N152" s="1"/>
-      <c r="O152" s="1" t="s">
-        <v>670</v>
-      </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>671</v>
+        <v>716</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="F153" s="10" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="K153" s="1" t="s">
-        <v>672</v>
+        <v>149</v>
+      </c>
+      <c r="F153" s="12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K153" s="2" t="s">
+        <v>717</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>673</v>
+        <v>718</v>
       </c>
       <c r="M153" s="1" t="s">
-        <v>674</v>
+        <v>719</v>
       </c>
       <c r="N153" s="1"/>
-      <c r="O153" s="1" t="s">
-        <v>675</v>
-      </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>676</v>
+        <v>720</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="F154" s="10" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="K154" s="1" t="s">
-        <v>677</v>
+        <v>721</v>
+      </c>
+      <c r="F154" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K154" s="2" t="s">
+        <v>722</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>678</v>
+        <v>723</v>
       </c>
       <c r="M154" s="1" t="s">
-        <v>679</v>
+        <v>724</v>
       </c>
       <c r="N154" s="1"/>
-      <c r="O154" s="1" t="s">
-        <v>680</v>
-      </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>681</v>
+        <v>725</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="F155" s="10" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="K155" s="1" t="s">
-        <v>683</v>
+        <v>726</v>
+      </c>
+      <c r="F155" s="12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K155" s="2" t="s">
+        <v>727</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>684</v>
+        <v>728</v>
       </c>
       <c r="M155" s="1" t="s">
-        <v>685</v>
+        <v>729</v>
       </c>
       <c r="N155" s="1"/>
       <c r="O155" s="1" t="s">
-        <v>686</v>
+        <v>730</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>687</v>
+        <v>731</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="F156" s="10" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="K156" s="1" t="s">
-        <v>689</v>
+        <v>726</v>
+      </c>
+      <c r="F156" s="12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K156" s="2" t="s">
+        <v>732</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>690</v>
+        <v>733</v>
       </c>
       <c r="M156" s="1" t="s">
-        <v>691</v>
+        <v>734</v>
       </c>
       <c r="N156" s="1"/>
+      <c r="O156" s="1" t="s">
+        <v>735</v>
+      </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="F157" s="12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K157" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="F157" s="10" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="K157" s="1" t="s">
+      <c r="L157" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="L157" s="1" t="s">
+      <c r="M157" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="M157" s="1" t="s">
+      <c r="N157" s="1"/>
+      <c r="O157" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="N157" s="1"/>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>687</v>
+        <v>737</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="F158" s="10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="K158" s="1" t="s">
-        <v>689</v>
+        <v>726</v>
+      </c>
+      <c r="F158" s="12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K158" s="2" t="s">
+        <v>738</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>690</v>
+        <v>739</v>
       </c>
       <c r="M158" s="1" t="s">
-        <v>691</v>
+        <v>740</v>
       </c>
       <c r="N158" s="1"/>
+      <c r="O158" s="1" t="s">
+        <v>741</v>
+      </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>692</v>
+        <v>742</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="F159" s="10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="K159" s="1" t="s">
-        <v>693</v>
+        <v>726</v>
+      </c>
+      <c r="F159" s="12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K159" s="2" t="s">
+        <v>743</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>694</v>
+        <v>744</v>
       </c>
       <c r="M159" s="1" t="s">
-        <v>695</v>
+        <v>745</v>
       </c>
       <c r="N159" s="1"/>
+      <c r="O159" s="1" t="s">
+        <v>746</v>
+      </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="F160" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K160" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="L160" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="M160" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="N160" s="1"/>
+      <c r="K160" s="2"/>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="F161" s="10" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K161" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="L161" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="M161" s="1" t="s">
-        <v>706</v>
-      </c>
-      <c r="N161" s="1"/>
-      <c r="O161" s="1" t="s">
-        <v>707</v>
-      </c>
+      <c r="K161" s="2"/>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="F162" s="10" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K162" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="L162" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="M162" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="N162" s="1"/>
-      <c r="O162" s="1" t="s">
-        <v>712</v>
-      </c>
+      <c r="K162" s="2"/>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="F163" s="10" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K163" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="L163" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="M163" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="N163" s="1"/>
-      <c r="O163" s="1" t="s">
-        <v>670</v>
-      </c>
+      <c r="K163" s="2"/>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="F164" s="10" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K164" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="L164" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="M164" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="N164" s="1"/>
-      <c r="O164" s="1" t="s">
-        <v>718</v>
-      </c>
+      <c r="K164" s="2"/>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="1" t="s">
-        <v>719</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="F165" s="10" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K165" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="L165" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="M165" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="N165" s="1"/>
-      <c r="O165" s="1" t="s">
-        <v>723</v>
-      </c>
+      <c r="K165" s="2"/>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K166" s="2"/>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K167" s="2"/>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K168" s="2"/>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K169" s="2"/>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K170" s="2"/>
+    </row>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K171" s="2"/>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K172" s="2"/>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K173" s="2"/>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K174" s="2"/>
+    </row>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K175" s="2"/>
+    </row>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K176" s="2"/>
+    </row>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K177" s="2"/>
+    </row>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K178" s="2"/>
+    </row>
+    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K179" s="2"/>
+    </row>
+    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K180" s="2"/>
+    </row>
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K181" s="2"/>
+    </row>
+    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K182" s="2"/>
+    </row>
+    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K183" s="2"/>
+    </row>
+    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K184" s="2"/>
+    </row>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K185" s="2"/>
+    </row>
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K186" s="2"/>
+    </row>
+    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K187" s="2"/>
+    </row>
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K188" s="2"/>
+    </row>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K189" s="2"/>
+    </row>
+    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K190" s="2"/>
+    </row>
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K191" s="2"/>
+    </row>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K192" s="2"/>
+    </row>
+    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K193" s="2"/>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K194" s="2"/>
+    </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K195" s="2"/>
+    </row>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K196" s="2"/>
+    </row>
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K197" s="2"/>
+    </row>
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K198" s="2"/>
+    </row>
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K199" s="2"/>
+    </row>
+    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K200" s="2"/>
+    </row>
+    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K201" s="2"/>
+    </row>
+    <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K202" s="2"/>
+    </row>
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K203" s="2"/>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K204" s="2"/>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K205" s="2"/>
+    </row>
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K206" s="2"/>
+    </row>
+    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K207" s="2"/>
+    </row>
+    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K208" s="2"/>
+    </row>
+    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K209" s="2"/>
+    </row>
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K210" s="2"/>
+    </row>
+    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K211" s="2"/>
+    </row>
+    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K212" s="2"/>
+    </row>
+    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K213" s="2"/>
+    </row>
+    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K214" s="2"/>
+    </row>
+    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K215" s="2"/>
+    </row>
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K216" s="2"/>
+    </row>
+    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K217" s="2"/>
+    </row>
+    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K218" s="2"/>
+    </row>
+    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K219" s="2"/>
+    </row>
+    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K220" s="2"/>
+    </row>
+    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K221" s="2"/>
+    </row>
+    <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K222" s="2"/>
+    </row>
+    <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K223" s="2"/>
+    </row>
+    <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K224" s="2"/>
+    </row>
+    <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K225" s="2"/>
+    </row>
+    <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K226" s="2"/>
+    </row>
+    <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K227" s="2"/>
+    </row>
+    <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K228" s="2"/>
+    </row>
+    <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K229" s="2"/>
+    </row>
+    <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K230" s="2"/>
+    </row>
+    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K231" s="2"/>
+    </row>
+    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K232" s="2"/>
+    </row>
+    <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K233" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7567,7 +7848,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -7618,538 +7899,538 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>641</v>
+        <v>666</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>582</v>
+        <v>404</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>3.89</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>642</v>
+        <v>667</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>643</v>
+        <v>668</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>644</v>
+        <v>669</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>582</v>
+        <v>404</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>3.89</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>647</v>
+        <v>672</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>648</v>
+        <v>673</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>649</v>
+        <v>674</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>650</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>651</v>
+        <v>676</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>582</v>
+        <v>404</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>3.89</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>652</v>
+        <v>677</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>653</v>
+        <v>678</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>654</v>
+        <v>679</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>655</v>
+        <v>680</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>656</v>
+        <v>681</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>725</v>
+        <v>748</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>582</v>
+        <v>404</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>3.89</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>657</v>
+        <v>682</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>658</v>
+        <v>683</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>659</v>
+        <v>684</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>660</v>
+        <v>685</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>661</v>
+        <v>686</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>582</v>
+        <v>404</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>3.89</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>662</v>
+        <v>687</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>663</v>
+        <v>688</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>664</v>
+        <v>689</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>665</v>
+        <v>690</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>666</v>
+        <v>691</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>582</v>
+        <v>404</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>3.89</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>667</v>
+        <v>692</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>668</v>
+        <v>693</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>669</v>
+        <v>694</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>670</v>
+        <v>695</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>671</v>
+        <v>696</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>582</v>
+        <v>404</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>3.89</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>676</v>
+        <v>701</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>582</v>
+        <v>404</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>3.89</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>677</v>
+        <v>702</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>678</v>
+        <v>703</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>679</v>
+        <v>704</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>680</v>
+        <v>705</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>681</v>
+        <v>706</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>682</v>
+        <v>561</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>3.11</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>683</v>
+        <v>707</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>684</v>
+        <v>708</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>685</v>
+        <v>709</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>686</v>
+        <v>710</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>687</v>
+        <v>711</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>726</v>
+        <v>749</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>688</v>
+        <v>750</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>3.33</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>689</v>
+        <v>713</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>690</v>
+        <v>714</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>691</v>
+        <v>715</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>692</v>
+        <v>716</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>726</v>
+        <v>749</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>688</v>
+        <v>750</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>3.33</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>693</v>
+        <v>717</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>694</v>
+        <v>718</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>695</v>
+        <v>719</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>687</v>
+        <v>711</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>726</v>
+        <v>749</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>696</v>
+        <v>751</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>1.11</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>689</v>
+        <v>713</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>690</v>
+        <v>714</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>691</v>
+        <v>715</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>692</v>
+        <v>716</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>726</v>
+        <v>749</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>696</v>
+        <v>751</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>1.11</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>693</v>
+        <v>717</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>694</v>
+        <v>718</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>695</v>
+        <v>719</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>697</v>
+        <v>720</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>698</v>
+        <v>721</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>5</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>699</v>
+        <v>722</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>700</v>
+        <v>723</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>701</v>
+        <v>724</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>702</v>
+        <v>725</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>703</v>
+        <v>726</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>2.78</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>704</v>
+        <v>727</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>705</v>
+        <v>728</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>706</v>
+        <v>729</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>707</v>
+        <v>730</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>708</v>
+        <v>731</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>703</v>
+        <v>726</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>2.78</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>709</v>
+        <v>732</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>710</v>
+        <v>733</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>711</v>
+        <v>734</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>712</v>
+        <v>735</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>713</v>
+        <v>736</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>703</v>
+        <v>726</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>2.78</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>667</v>
+        <v>692</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>668</v>
+        <v>693</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>669</v>
+        <v>694</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>670</v>
+        <v>695</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>714</v>
+        <v>737</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>703</v>
+        <v>726</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>2.78</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>715</v>
+        <v>738</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>716</v>
+        <v>739</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>717</v>
+        <v>740</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>718</v>
+        <v>741</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>719</v>
+        <v>742</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>703</v>
+        <v>726</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>2.78</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>720</v>
+        <v>743</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>721</v>
+        <v>744</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>722</v>
+        <v>745</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>723</v>
+        <v>746</v>
       </c>
     </row>
   </sheetData>
